--- a/research/traditional_assets/database/data/south_africa/south_africa_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_homebuilding.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1263843126866621</v>
+        <v>0.1260759250424081</v>
       </c>
       <c r="C2">
-        <v>224.4171680704228</v>
+        <v>222.8726582261674</v>
       </c>
       <c r="D2">
-        <v>210.7171680704228</v>
+        <v>211.5266582261674</v>
       </c>
       <c r="E2">
-        <v>-172.9</v>
+        <v>-170.546</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.354</v>
       </c>
       <c r="G2">
         <v>13.7</v>
@@ -1445,28 +1445,28 @@
         <v>16.929</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1184062</v>
       </c>
       <c r="N2">
-        <v>16.929</v>
+        <v>16.8105938</v>
       </c>
       <c r="O2">
-        <v>4.57083</v>
+        <v>4.538860326</v>
       </c>
       <c r="P2">
-        <v>12.35817</v>
+        <v>12.271733474</v>
       </c>
       <c r="Q2">
-        <v>12.30417</v>
+        <v>12.217733474</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1263843126866621</v>
+        <v>0.1269785202448567</v>
       </c>
       <c r="T2">
-        <v>0.9653793013859414</v>
+        <v>0.9724977548204035</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>142.9739321082849</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1260759250424081</v>
+        <v>0.1257675373981542</v>
       </c>
       <c r="C3">
-        <v>222.8726582261674</v>
+        <v>221.3343918344501</v>
       </c>
       <c r="D3">
-        <v>211.5266582261674</v>
+        <v>212.3423918344501</v>
       </c>
       <c r="E3">
-        <v>-170.546</v>
+        <v>-168.192</v>
       </c>
       <c r="F3">
-        <v>2.354</v>
+        <v>4.708</v>
       </c>
       <c r="G3">
         <v>13.7</v>
@@ -1527,28 +1527,28 @@
         <v>16.929</v>
       </c>
       <c r="M3">
-        <v>0.1184062</v>
+        <v>0.2368124</v>
       </c>
       <c r="N3">
-        <v>16.8105938</v>
+        <v>16.6921876</v>
       </c>
       <c r="O3">
-        <v>4.538860326</v>
+        <v>4.506890651999999</v>
       </c>
       <c r="P3">
-        <v>12.271733474</v>
+        <v>12.185296948</v>
       </c>
       <c r="Q3">
-        <v>12.217733474</v>
+        <v>12.131296948</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1269785202448567</v>
+        <v>0.1275848544879124</v>
       </c>
       <c r="T3">
-        <v>0.9724977548204035</v>
+        <v>0.9797614828147524</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>142.9739321082849</v>
+        <v>71.48696605414241</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1257675373981542</v>
+        <v>0.1254591497539002</v>
       </c>
       <c r="C4">
-        <v>221.3343918344501</v>
+        <v>219.8024414068519</v>
       </c>
       <c r="D4">
-        <v>212.3423918344501</v>
+        <v>213.1644414068519</v>
       </c>
       <c r="E4">
-        <v>-168.192</v>
+        <v>-165.838</v>
       </c>
       <c r="F4">
-        <v>4.708</v>
+        <v>7.062</v>
       </c>
       <c r="G4">
         <v>13.7</v>
@@ -1609,28 +1609,28 @@
         <v>16.929</v>
       </c>
       <c r="M4">
-        <v>0.2368124</v>
+        <v>0.3552186</v>
       </c>
       <c r="N4">
-        <v>16.6921876</v>
+        <v>16.5737814</v>
       </c>
       <c r="O4">
-        <v>4.506890651999999</v>
+        <v>4.474920978</v>
       </c>
       <c r="P4">
-        <v>12.185296948</v>
+        <v>12.098860422</v>
       </c>
       <c r="Q4">
-        <v>12.131296948</v>
+        <v>12.044860422</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1275848544879124</v>
+        <v>0.1282036904679383</v>
       </c>
       <c r="T4">
-        <v>0.9797614828147524</v>
+        <v>0.9871749783966137</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>71.48696605414241</v>
+        <v>47.65797736942829</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1254591497539002</v>
+        <v>0.1251507621096462</v>
       </c>
       <c r="C5">
-        <v>219.8024414068519</v>
+        <v>218.276880582185</v>
       </c>
       <c r="D5">
-        <v>213.1644414068519</v>
+        <v>213.992880582185</v>
       </c>
       <c r="E5">
-        <v>-165.838</v>
+        <v>-163.484</v>
       </c>
       <c r="F5">
-        <v>7.062</v>
+        <v>9.416</v>
       </c>
       <c r="G5">
         <v>13.7</v>
@@ -1691,28 +1691,28 @@
         <v>16.929</v>
       </c>
       <c r="M5">
-        <v>0.3552186</v>
+        <v>0.4736248</v>
       </c>
       <c r="N5">
-        <v>16.5737814</v>
+        <v>16.4553752</v>
       </c>
       <c r="O5">
-        <v>4.474920978</v>
+        <v>4.442951304</v>
       </c>
       <c r="P5">
-        <v>12.098860422</v>
+        <v>12.012423896</v>
       </c>
       <c r="Q5">
-        <v>12.044860422</v>
+        <v>11.958423896</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1282036904679383</v>
+        <v>0.1288354188642148</v>
       </c>
       <c r="T5">
-        <v>0.9871749783966137</v>
+        <v>0.9947429218030972</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.65797736942829</v>
+        <v>35.74348302707121</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1251507621096462</v>
+        <v>0.1248423744653922</v>
       </c>
       <c r="C6">
-        <v>218.276880582185</v>
+        <v>216.7577841484837</v>
       </c>
       <c r="D6">
-        <v>213.992880582185</v>
+        <v>214.8277841484837</v>
       </c>
       <c r="E6">
-        <v>-163.484</v>
+        <v>-161.13</v>
       </c>
       <c r="F6">
-        <v>9.416</v>
+        <v>11.77</v>
       </c>
       <c r="G6">
         <v>13.7</v>
@@ -1773,28 +1773,28 @@
         <v>16.929</v>
       </c>
       <c r="M6">
-        <v>0.4736248</v>
+        <v>0.5920310000000001</v>
       </c>
       <c r="N6">
-        <v>16.4553752</v>
+        <v>16.336969</v>
       </c>
       <c r="O6">
-        <v>4.442951304</v>
+        <v>4.41098163</v>
       </c>
       <c r="P6">
-        <v>12.012423896</v>
+        <v>11.92598737</v>
       </c>
       <c r="Q6">
-        <v>11.958423896</v>
+        <v>11.87198737</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1288354188642148</v>
+        <v>0.129480446805676</v>
       </c>
       <c r="T6">
-        <v>0.9947429218030972</v>
+        <v>1.002470190333927</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.74348302707121</v>
+        <v>28.59478642165697</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1248423744653922</v>
+        <v>0.1245339868211382</v>
       </c>
       <c r="C7">
-        <v>216.7577841484837</v>
+        <v>215.2452280655097</v>
       </c>
       <c r="D7">
-        <v>214.8277841484837</v>
+        <v>215.6692280655097</v>
       </c>
       <c r="E7">
-        <v>-161.13</v>
+        <v>-158.776</v>
       </c>
       <c r="F7">
-        <v>11.77</v>
+        <v>14.124</v>
       </c>
       <c r="G7">
         <v>13.7</v>
@@ -1855,28 +1855,28 @@
         <v>16.929</v>
       </c>
       <c r="M7">
-        <v>0.5920310000000001</v>
+        <v>0.7104372000000001</v>
       </c>
       <c r="N7">
-        <v>16.336969</v>
+        <v>16.2185628</v>
       </c>
       <c r="O7">
-        <v>4.41098163</v>
+        <v>4.379011955999999</v>
       </c>
       <c r="P7">
-        <v>11.92598737</v>
+        <v>11.839550844</v>
       </c>
       <c r="Q7">
-        <v>11.87198737</v>
+        <v>11.785550844</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.129480446805676</v>
+        <v>0.1301391987458917</v>
       </c>
       <c r="T7">
-        <v>1.002470190333927</v>
+        <v>1.010361868833499</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.59478642165697</v>
+        <v>23.82898868471414</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1245339868211382</v>
+        <v>0.1242255991768842</v>
       </c>
       <c r="C8">
-        <v>215.2452280655097</v>
+        <v>213.7392894877908</v>
       </c>
       <c r="D8">
-        <v>215.6692280655097</v>
+        <v>216.5172894877908</v>
       </c>
       <c r="E8">
-        <v>-158.776</v>
+        <v>-156.422</v>
       </c>
       <c r="F8">
-        <v>14.124</v>
+        <v>16.478</v>
       </c>
       <c r="G8">
         <v>13.7</v>
@@ -1937,28 +1937,28 @@
         <v>16.929</v>
       </c>
       <c r="M8">
-        <v>0.7104372</v>
+        <v>0.8288433999999999</v>
       </c>
       <c r="N8">
-        <v>16.2185628</v>
+        <v>16.1001566</v>
       </c>
       <c r="O8">
-        <v>4.379011955999999</v>
+        <v>4.347042281999999</v>
       </c>
       <c r="P8">
-        <v>11.839550844</v>
+        <v>11.753114318</v>
       </c>
       <c r="Q8">
-        <v>11.785550844</v>
+        <v>11.699114318</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1301391987458917</v>
+        <v>0.1308121173944992</v>
       </c>
       <c r="T8">
-        <v>1.010361868833499</v>
+        <v>1.018423260849191</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.82898868471414</v>
+        <v>20.4248474440407</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1242255991768842</v>
+        <v>0.1239172115326302</v>
       </c>
       <c r="C9">
-        <v>213.7392894877909</v>
+        <v>212.2400467882035</v>
       </c>
       <c r="D9">
-        <v>216.5172894877909</v>
+        <v>217.3720467882035</v>
       </c>
       <c r="E9">
-        <v>-156.422</v>
+        <v>-154.068</v>
       </c>
       <c r="F9">
-        <v>16.478</v>
+        <v>18.832</v>
       </c>
       <c r="G9">
         <v>13.7</v>
@@ -2019,28 +2019,28 @@
         <v>16.929</v>
       </c>
       <c r="M9">
-        <v>0.8288434</v>
+        <v>0.9472496</v>
       </c>
       <c r="N9">
-        <v>16.1001566</v>
+        <v>15.9817504</v>
       </c>
       <c r="O9">
-        <v>4.347042281999999</v>
+        <v>4.315072608</v>
       </c>
       <c r="P9">
-        <v>11.753114318</v>
+        <v>11.666677792</v>
       </c>
       <c r="Q9">
-        <v>11.699114318</v>
+        <v>11.612677792</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1308121173944992</v>
+        <v>0.1314996647093807</v>
       </c>
       <c r="T9">
-        <v>1.018423260849191</v>
+        <v>1.026659900517397</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.42484744404069</v>
+        <v>17.87174151353561</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1239172115326302</v>
+        <v>0.1236088238883763</v>
       </c>
       <c r="C10">
-        <v>212.2400467882035</v>
+        <v>210.747579582117</v>
       </c>
       <c r="D10">
-        <v>217.3720467882035</v>
+        <v>218.233579582117</v>
       </c>
       <c r="E10">
-        <v>-154.068</v>
+        <v>-151.714</v>
       </c>
       <c r="F10">
-        <v>18.832</v>
+        <v>21.186</v>
       </c>
       <c r="G10">
         <v>13.7</v>
@@ -2101,28 +2101,28 @@
         <v>16.929</v>
       </c>
       <c r="M10">
-        <v>0.9472496</v>
+        <v>1.0656558</v>
       </c>
       <c r="N10">
-        <v>15.9817504</v>
+        <v>15.8633442</v>
       </c>
       <c r="O10">
-        <v>4.315072608</v>
+        <v>4.283102934</v>
       </c>
       <c r="P10">
-        <v>11.666677792</v>
+        <v>11.580241266</v>
       </c>
       <c r="Q10">
-        <v>11.612677792</v>
+        <v>11.526241266</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1314996647093807</v>
+        <v>0.1322023229542596</v>
       </c>
       <c r="T10">
-        <v>1.026659900517397</v>
+        <v>1.035077565233256</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.87174151353561</v>
+        <v>15.88599245647609</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1236088238883763</v>
+        <v>0.1233004362441222</v>
       </c>
       <c r="C11">
-        <v>210.747579582117</v>
+        <v>209.2619687521142</v>
       </c>
       <c r="D11">
-        <v>218.233579582117</v>
+        <v>219.1019687521142</v>
       </c>
       <c r="E11">
-        <v>-151.714</v>
+        <v>-149.36</v>
       </c>
       <c r="F11">
-        <v>21.186</v>
+        <v>23.54</v>
       </c>
       <c r="G11">
         <v>13.7</v>
@@ -2183,28 +2183,28 @@
         <v>16.929</v>
       </c>
       <c r="M11">
-        <v>1.0656558</v>
+        <v>1.184062</v>
       </c>
       <c r="N11">
-        <v>15.8633442</v>
+        <v>15.744938</v>
       </c>
       <c r="O11">
-        <v>4.283102934</v>
+        <v>4.25113326</v>
       </c>
       <c r="P11">
-        <v>11.580241266</v>
+        <v>11.49380474</v>
       </c>
       <c r="Q11">
-        <v>11.526241266</v>
+        <v>11.43980474</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1322023229542596</v>
+        <v>0.1329205958268025</v>
       </c>
       <c r="T11">
-        <v>1.035077565233256</v>
+        <v>1.043682289165023</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.88599245647609</v>
+        <v>14.29739321082848</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1233004362441222</v>
+        <v>0.1229920485998683</v>
       </c>
       <c r="C12">
-        <v>209.2619687521142</v>
+        <v>207.7832964733037</v>
       </c>
       <c r="D12">
-        <v>219.1019687521142</v>
+        <v>219.9772964733037</v>
       </c>
       <c r="E12">
-        <v>-149.36</v>
+        <v>-147.006</v>
       </c>
       <c r="F12">
-        <v>23.54</v>
+        <v>25.894</v>
       </c>
       <c r="G12">
         <v>13.7</v>
@@ -2265,28 +2265,28 @@
         <v>16.929</v>
       </c>
       <c r="M12">
-        <v>1.184062</v>
+        <v>1.3024682</v>
       </c>
       <c r="N12">
-        <v>15.744938</v>
+        <v>15.6265318</v>
       </c>
       <c r="O12">
-        <v>4.25113326</v>
+        <v>4.219163586</v>
       </c>
       <c r="P12">
-        <v>11.49380474</v>
+        <v>11.407368214</v>
       </c>
       <c r="Q12">
-        <v>11.43980474</v>
+        <v>11.353368214</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1329205958268025</v>
+        <v>0.1336550096627733</v>
       </c>
       <c r="T12">
-        <v>1.043682289165023</v>
+        <v>1.052480377679527</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.29739321082848</v>
+        <v>12.99763019166226</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1229920485998683</v>
+        <v>0.1228150609556143</v>
       </c>
       <c r="C13">
-        <v>207.7832964733037</v>
+        <v>205.9348243922468</v>
       </c>
       <c r="D13">
-        <v>219.9772964733037</v>
+        <v>220.4828243922468</v>
       </c>
       <c r="E13">
-        <v>-147.006</v>
+        <v>-144.652</v>
       </c>
       <c r="F13">
-        <v>25.894</v>
+        <v>28.248</v>
       </c>
       <c r="G13">
         <v>13.7</v>
@@ -2347,45 +2347,45 @@
         <v>16.929</v>
       </c>
       <c r="M13">
-        <v>1.3024682</v>
+        <v>1.4632464</v>
       </c>
       <c r="N13">
-        <v>15.6265318</v>
+        <v>15.4657536</v>
       </c>
       <c r="O13">
-        <v>4.219163586</v>
+        <v>4.175753472</v>
       </c>
       <c r="P13">
-        <v>11.407368214</v>
+        <v>11.290000128</v>
       </c>
       <c r="Q13">
-        <v>11.353368214</v>
+        <v>11.236000128</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1336550096627733</v>
+        <v>0.134406114722289</v>
       </c>
       <c r="T13">
-        <v>1.052480377679527</v>
+        <v>1.061478422751178</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>12.99763019166226</v>
+        <v>11.56948002742395</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1228150609556143</v>
+        <v>0.1225176233113603</v>
       </c>
       <c r="C14">
-        <v>205.9348243922468</v>
+        <v>204.4356461275284</v>
       </c>
       <c r="D14">
-        <v>220.4828243922468</v>
+        <v>221.3376461275284</v>
       </c>
       <c r="E14">
-        <v>-144.652</v>
+        <v>-142.298</v>
       </c>
       <c r="F14">
-        <v>28.248</v>
+        <v>30.602</v>
       </c>
       <c r="G14">
         <v>13.7</v>
@@ -2429,28 +2429,28 @@
         <v>16.929</v>
       </c>
       <c r="M14">
-        <v>1.4632464</v>
+        <v>1.5851836</v>
       </c>
       <c r="N14">
-        <v>15.4657536</v>
+        <v>15.3438164</v>
       </c>
       <c r="O14">
-        <v>4.175753472</v>
+        <v>4.142830428</v>
       </c>
       <c r="P14">
-        <v>11.290000128</v>
+        <v>11.200985972</v>
       </c>
       <c r="Q14">
-        <v>11.236000128</v>
+        <v>11.146985972</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.134406114722289</v>
+        <v>0.135174486564782</v>
       </c>
       <c r="T14">
-        <v>1.061478422751178</v>
+        <v>1.070683319433672</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.56948002742395</v>
+        <v>10.67952002531442</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1225176233113603</v>
+        <v>0.1222201856671063</v>
       </c>
       <c r="C15">
-        <v>204.4356461275284</v>
+        <v>202.9431220252144</v>
       </c>
       <c r="D15">
-        <v>221.3376461275284</v>
+        <v>222.1991220252144</v>
       </c>
       <c r="E15">
-        <v>-142.298</v>
+        <v>-139.944</v>
       </c>
       <c r="F15">
-        <v>30.602</v>
+        <v>32.956</v>
       </c>
       <c r="G15">
         <v>13.7</v>
@@ -2511,28 +2511,28 @@
         <v>16.929</v>
       </c>
       <c r="M15">
-        <v>1.5851836</v>
+        <v>1.7071208</v>
       </c>
       <c r="N15">
-        <v>15.3438164</v>
+        <v>15.2218792</v>
       </c>
       <c r="O15">
-        <v>4.142830428</v>
+        <v>4.109907384</v>
       </c>
       <c r="P15">
-        <v>11.200985972</v>
+        <v>11.111971816</v>
       </c>
       <c r="Q15">
-        <v>11.146985972</v>
+        <v>11.057971816</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.135174486564782</v>
+        <v>0.1359607275198911</v>
       </c>
       <c r="T15">
-        <v>1.070683319433672</v>
+        <v>1.080102283480875</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.67952002531442</v>
+        <v>9.916697166363386</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1222201856671063</v>
+        <v>0.1221088980228523</v>
       </c>
       <c r="C16">
-        <v>202.9431220252144</v>
+        <v>200.9131735773425</v>
       </c>
       <c r="D16">
-        <v>222.1991220252144</v>
+        <v>222.5231735773425</v>
       </c>
       <c r="E16">
-        <v>-139.944</v>
+        <v>-137.59</v>
       </c>
       <c r="F16">
-        <v>32.956</v>
+        <v>35.31000000000001</v>
       </c>
       <c r="G16">
         <v>13.7</v>
@@ -2593,45 +2593,45 @@
         <v>16.929</v>
       </c>
       <c r="M16">
-        <v>1.7071208</v>
+        <v>1.889085000000001</v>
       </c>
       <c r="N16">
-        <v>15.2218792</v>
+        <v>15.039915</v>
       </c>
       <c r="O16">
-        <v>4.109907384</v>
+        <v>4.06077705</v>
       </c>
       <c r="P16">
-        <v>11.111971816</v>
+        <v>10.97913795</v>
       </c>
       <c r="Q16">
-        <v>11.057971816</v>
+        <v>10.92513795</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1359607275198911</v>
+        <v>0.1367654682621792</v>
       </c>
       <c r="T16">
-        <v>1.080102283480875</v>
+        <v>1.089742870211542</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.916697166363386</v>
+        <v>8.961481352083148</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1221088980228523</v>
+        <v>0.1218238703785983</v>
       </c>
       <c r="C17">
-        <v>200.9131735773425</v>
+        <v>199.3934543846838</v>
       </c>
       <c r="D17">
-        <v>222.5231735773425</v>
+        <v>223.3574543846838</v>
       </c>
       <c r="E17">
-        <v>-137.59</v>
+        <v>-135.236</v>
       </c>
       <c r="F17">
-        <v>35.31</v>
+        <v>37.664</v>
       </c>
       <c r="G17">
         <v>13.7</v>
@@ -2675,28 +2675,28 @@
         <v>16.929</v>
       </c>
       <c r="M17">
-        <v>1.889085</v>
+        <v>2.015024</v>
       </c>
       <c r="N17">
-        <v>15.039915</v>
+        <v>14.913976</v>
       </c>
       <c r="O17">
-        <v>4.06077705</v>
+        <v>4.02677352</v>
       </c>
       <c r="P17">
-        <v>10.97913795</v>
+        <v>10.88720248</v>
       </c>
       <c r="Q17">
-        <v>10.92513795</v>
+        <v>10.83320248</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1367654682621792</v>
+        <v>0.1375893694983314</v>
       </c>
       <c r="T17">
-        <v>1.089742870211542</v>
+        <v>1.099612994721511</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.961481352083151</v>
+        <v>8.401388767577954</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1218238703785983</v>
+        <v>0.1215388427343444</v>
       </c>
       <c r="C18">
-        <v>199.3934543846838</v>
+        <v>197.8800144824019</v>
       </c>
       <c r="D18">
-        <v>223.3574543846838</v>
+        <v>224.1980144824019</v>
       </c>
       <c r="E18">
-        <v>-135.236</v>
+        <v>-132.882</v>
       </c>
       <c r="F18">
-        <v>37.664</v>
+        <v>40.018</v>
       </c>
       <c r="G18">
         <v>13.7</v>
@@ -2757,28 +2757,28 @@
         <v>16.929</v>
       </c>
       <c r="M18">
-        <v>2.015024</v>
+        <v>2.140963</v>
       </c>
       <c r="N18">
-        <v>14.913976</v>
+        <v>14.788037</v>
       </c>
       <c r="O18">
-        <v>4.02677352</v>
+        <v>3.99276999</v>
       </c>
       <c r="P18">
-        <v>10.88720248</v>
+        <v>10.79526701</v>
       </c>
       <c r="Q18">
-        <v>10.83320248</v>
+        <v>10.74126701</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1375893694983314</v>
+        <v>0.1384331237763185</v>
       </c>
       <c r="T18">
-        <v>1.099612994721511</v>
+        <v>1.10972095355702</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.401388767577954</v>
+        <v>7.907189428308662</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1215388427343444</v>
+        <v>0.1213589350900903</v>
       </c>
       <c r="C19">
-        <v>197.8800144824019</v>
+        <v>196.0598353545973</v>
       </c>
       <c r="D19">
-        <v>224.1980144824019</v>
+        <v>224.7318353545974</v>
       </c>
       <c r="E19">
-        <v>-132.882</v>
+        <v>-130.528</v>
       </c>
       <c r="F19">
-        <v>40.018</v>
+        <v>42.37200000000001</v>
       </c>
       <c r="G19">
         <v>13.7</v>
@@ -2839,45 +2839,45 @@
         <v>16.929</v>
       </c>
       <c r="M19">
-        <v>2.140963</v>
+        <v>2.3007996</v>
       </c>
       <c r="N19">
-        <v>14.788037</v>
+        <v>14.6282004</v>
       </c>
       <c r="O19">
-        <v>3.99276999</v>
+        <v>3.949614108</v>
       </c>
       <c r="P19">
-        <v>10.79526701</v>
+        <v>10.678586292</v>
       </c>
       <c r="Q19">
-        <v>10.74126701</v>
+        <v>10.624586292</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1384331237763185</v>
+        <v>0.1392974574269394</v>
       </c>
       <c r="T19">
-        <v>1.10972095355702</v>
+        <v>1.120075447973884</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.907189428308662</v>
+        <v>7.35787680074353</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1213589350900904</v>
+        <v>0.1210797474458364</v>
       </c>
       <c r="C20">
-        <v>196.0598353545973</v>
+        <v>194.5392912817265</v>
       </c>
       <c r="D20">
-        <v>224.7318353545973</v>
+        <v>225.5652912817266</v>
       </c>
       <c r="E20">
-        <v>-130.528</v>
+        <v>-128.174</v>
       </c>
       <c r="F20">
-        <v>42.372</v>
+        <v>44.726</v>
       </c>
       <c r="G20">
         <v>13.7</v>
@@ -2921,28 +2921,28 @@
         <v>16.929</v>
       </c>
       <c r="M20">
-        <v>2.3007996</v>
+        <v>2.4286218</v>
       </c>
       <c r="N20">
-        <v>14.6282004</v>
+        <v>14.5003782</v>
       </c>
       <c r="O20">
-        <v>3.949614108</v>
+        <v>3.915102114</v>
       </c>
       <c r="P20">
-        <v>10.678586292</v>
+        <v>10.585276086</v>
       </c>
       <c r="Q20">
-        <v>10.624586292</v>
+        <v>10.531276086</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1392974574269394</v>
+        <v>0.1401831326491807</v>
       </c>
       <c r="T20">
-        <v>1.120075447973884</v>
+        <v>1.130685608919559</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.357876800743533</v>
+        <v>6.970620127020188</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1210797474458364</v>
+        <v>0.1208005598015824</v>
       </c>
       <c r="C21">
-        <v>194.5392912817265</v>
+        <v>193.0249522451248</v>
       </c>
       <c r="D21">
-        <v>225.5652912817266</v>
+        <v>226.4049522451249</v>
       </c>
       <c r="E21">
-        <v>-128.174</v>
+        <v>-125.82</v>
       </c>
       <c r="F21">
-        <v>44.726</v>
+        <v>47.08000000000001</v>
       </c>
       <c r="G21">
         <v>13.7</v>
@@ -3003,28 +3003,28 @@
         <v>16.929</v>
       </c>
       <c r="M21">
-        <v>2.4286218</v>
+        <v>2.556444</v>
       </c>
       <c r="N21">
-        <v>14.5003782</v>
+        <v>14.372556</v>
       </c>
       <c r="O21">
-        <v>3.915102114</v>
+        <v>3.880590119999999</v>
       </c>
       <c r="P21">
-        <v>10.585276086</v>
+        <v>10.49196588</v>
       </c>
       <c r="Q21">
-        <v>10.531276086</v>
+        <v>10.43796588</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1401831326491807</v>
+        <v>0.141090949751978</v>
       </c>
       <c r="T21">
-        <v>1.130685608919559</v>
+        <v>1.141561023888876</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.970620127020188</v>
+        <v>6.622089120669178</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1208005598015824</v>
+        <v>0.1205213721573284</v>
       </c>
       <c r="C22">
-        <v>193.0249522451248</v>
+        <v>191.5168877979632</v>
       </c>
       <c r="D22">
-        <v>226.4049522451249</v>
+        <v>227.2508877979632</v>
       </c>
       <c r="E22">
-        <v>-125.82</v>
+        <v>-123.466</v>
       </c>
       <c r="F22">
-        <v>47.08000000000001</v>
+        <v>49.434</v>
       </c>
       <c r="G22">
         <v>13.7</v>
@@ -3085,28 +3085,28 @@
         <v>16.929</v>
       </c>
       <c r="M22">
-        <v>2.556444</v>
+        <v>2.6842662</v>
       </c>
       <c r="N22">
-        <v>14.372556</v>
+        <v>14.2447338</v>
       </c>
       <c r="O22">
-        <v>3.880590119999999</v>
+        <v>3.846078126</v>
       </c>
       <c r="P22">
-        <v>10.49196588</v>
+        <v>10.398655674</v>
       </c>
       <c r="Q22">
-        <v>10.43796588</v>
+        <v>10.344655674</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.141090949751978</v>
+        <v>0.1420217495662385</v>
       </c>
       <c r="T22">
-        <v>1.141561023888876</v>
+        <v>1.152711765819441</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.622089120669178</v>
+        <v>6.306751543494456</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1205213721573284</v>
+        <v>0.1204027845130744</v>
       </c>
       <c r="C23">
-        <v>191.5168877979632</v>
+        <v>189.5241229397141</v>
       </c>
       <c r="D23">
-        <v>227.2508877979632</v>
+        <v>227.6121229397141</v>
       </c>
       <c r="E23">
-        <v>-123.466</v>
+        <v>-121.112</v>
       </c>
       <c r="F23">
-        <v>49.434</v>
+        <v>51.788</v>
       </c>
       <c r="G23">
         <v>13.7</v>
@@ -3167,45 +3167,45 @@
         <v>16.929</v>
       </c>
       <c r="M23">
-        <v>2.6842662</v>
+        <v>2.8638764</v>
       </c>
       <c r="N23">
-        <v>14.2447338</v>
+        <v>14.0651236</v>
       </c>
       <c r="O23">
-        <v>3.846078126</v>
+        <v>3.797583372</v>
       </c>
       <c r="P23">
-        <v>10.398655674</v>
+        <v>10.267540228</v>
       </c>
       <c r="Q23">
-        <v>10.344655674</v>
+        <v>10.213540228</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1420217495662385</v>
+        <v>0.1429764160424031</v>
       </c>
       <c r="T23">
-        <v>1.152711765819441</v>
+        <v>1.164148424209765</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.27</v>
       </c>
       <c r="W23">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.306751543494457</v>
+        <v>5.911218794218912</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1204027845130744</v>
+        <v>0.1201308968688204</v>
       </c>
       <c r="C24">
-        <v>189.5241229397141</v>
+        <v>188.0026828376384</v>
       </c>
       <c r="D24">
-        <v>227.6121229397141</v>
+        <v>228.4446828376384</v>
       </c>
       <c r="E24">
-        <v>-121.112</v>
+        <v>-118.758</v>
       </c>
       <c r="F24">
-        <v>51.788</v>
+        <v>54.142</v>
       </c>
       <c r="G24">
         <v>13.7</v>
@@ -3249,28 +3249,28 @@
         <v>16.929</v>
       </c>
       <c r="M24">
-        <v>2.8638764</v>
+        <v>2.9940526</v>
       </c>
       <c r="N24">
-        <v>14.0651236</v>
+        <v>13.9349474</v>
       </c>
       <c r="O24">
-        <v>3.797583372</v>
+        <v>3.762435798</v>
       </c>
       <c r="P24">
-        <v>10.267540228</v>
+        <v>10.172511602</v>
       </c>
       <c r="Q24">
-        <v>10.213540228</v>
+        <v>10.118511602</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1429764160424031</v>
+        <v>0.1439558790504161</v>
       </c>
       <c r="T24">
-        <v>1.164148424209765</v>
+        <v>1.175882138662175</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.911218794218912</v>
+        <v>5.654209281426785</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1201308968688204</v>
+        <v>0.1198590092245664</v>
       </c>
       <c r="C25">
-        <v>188.0026828376384</v>
+        <v>186.487355773037</v>
       </c>
       <c r="D25">
-        <v>228.4446828376384</v>
+        <v>229.283355773037</v>
       </c>
       <c r="E25">
-        <v>-118.758</v>
+        <v>-116.404</v>
       </c>
       <c r="F25">
-        <v>54.142</v>
+        <v>56.49600000000001</v>
       </c>
       <c r="G25">
         <v>13.7</v>
@@ -3331,28 +3331,28 @@
         <v>16.929</v>
       </c>
       <c r="M25">
-        <v>2.9940526</v>
+        <v>3.1242288</v>
       </c>
       <c r="N25">
-        <v>13.9349474</v>
+        <v>13.8047712</v>
       </c>
       <c r="O25">
-        <v>3.762435798</v>
+        <v>3.727288224</v>
       </c>
       <c r="P25">
-        <v>10.172511602</v>
+        <v>10.077482976</v>
       </c>
       <c r="Q25">
-        <v>10.118511602</v>
+        <v>10.023482976</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1439558790504161</v>
+        <v>0.1449611174007453</v>
       </c>
       <c r="T25">
-        <v>1.175882138662175</v>
+        <v>1.187924635073858</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.654209281426785</v>
+        <v>5.418617228034002</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1198590092245664</v>
+        <v>0.1195871215803124</v>
       </c>
       <c r="C26">
-        <v>186.487355773037</v>
+        <v>184.9782093210905</v>
       </c>
       <c r="D26">
-        <v>229.283355773037</v>
+        <v>230.1282093210905</v>
       </c>
       <c r="E26">
-        <v>-116.404</v>
+        <v>-114.05</v>
       </c>
       <c r="F26">
-        <v>56.496</v>
+        <v>58.85</v>
       </c>
       <c r="G26">
         <v>13.7</v>
@@ -3413,28 +3413,28 @@
         <v>16.929</v>
       </c>
       <c r="M26">
-        <v>3.1242288</v>
+        <v>3.254405</v>
       </c>
       <c r="N26">
-        <v>13.8047712</v>
+        <v>13.674595</v>
       </c>
       <c r="O26">
-        <v>3.727288224</v>
+        <v>3.69214065</v>
       </c>
       <c r="P26">
-        <v>10.077482976</v>
+        <v>9.982454349999998</v>
       </c>
       <c r="Q26">
-        <v>10.023482976</v>
+        <v>9.928454349999997</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1449611174007453</v>
+        <v>0.1459931621070832</v>
       </c>
       <c r="T26">
-        <v>1.187924635073858</v>
+        <v>1.200288264723187</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.418617228034003</v>
+        <v>5.201872538912642</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1195871215803124</v>
+        <v>0.1193152339360584</v>
       </c>
       <c r="C27">
-        <v>184.9782093210905</v>
+        <v>183.4753120566557</v>
       </c>
       <c r="D27">
-        <v>230.1282093210905</v>
+        <v>230.9793120566557</v>
       </c>
       <c r="E27">
-        <v>-114.05</v>
+        <v>-111.696</v>
       </c>
       <c r="F27">
-        <v>58.85</v>
+        <v>61.204</v>
       </c>
       <c r="G27">
         <v>13.7</v>
@@ -3495,28 +3495,28 @@
         <v>16.929</v>
       </c>
       <c r="M27">
-        <v>3.254405</v>
+        <v>3.3845812</v>
       </c>
       <c r="N27">
-        <v>13.674595</v>
+        <v>13.5444188</v>
       </c>
       <c r="O27">
-        <v>3.69214065</v>
+        <v>3.656993076</v>
       </c>
       <c r="P27">
-        <v>9.982454349999998</v>
+        <v>9.887425724</v>
       </c>
       <c r="Q27">
-        <v>9.928454349999997</v>
+        <v>9.833425724</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1459931621070832</v>
+        <v>0.1470530999135925</v>
       </c>
       <c r="T27">
-        <v>1.200288264723187</v>
+        <v>1.2129860465252</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.201872538912642</v>
+        <v>5.001800518185234</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1193152339360584</v>
+        <v>0.1190433462918045</v>
       </c>
       <c r="C28">
-        <v>183.4753120566557</v>
+        <v>181.9787335728203</v>
       </c>
       <c r="D28">
-        <v>230.9793120566557</v>
+        <v>231.8367335728203</v>
       </c>
       <c r="E28">
-        <v>-111.696</v>
+        <v>-109.342</v>
       </c>
       <c r="F28">
-        <v>61.204</v>
+        <v>63.55800000000001</v>
       </c>
       <c r="G28">
         <v>13.7</v>
@@ -3577,28 +3577,28 @@
         <v>16.929</v>
       </c>
       <c r="M28">
-        <v>3.3845812</v>
+        <v>3.514757400000001</v>
       </c>
       <c r="N28">
-        <v>13.5444188</v>
+        <v>13.4142426</v>
       </c>
       <c r="O28">
-        <v>3.656993076</v>
+        <v>3.621845502</v>
       </c>
       <c r="P28">
-        <v>9.887425724</v>
+        <v>9.792397097999999</v>
       </c>
       <c r="Q28">
-        <v>9.833425724</v>
+        <v>9.738397097999998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1470530999135925</v>
+        <v>0.1481420771120609</v>
       </c>
       <c r="T28">
-        <v>1.2129860465252</v>
+        <v>1.226031712760146</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.001800518185234</v>
+        <v>4.816548647141335</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1190433462918045</v>
+        <v>0.1187714586475505</v>
       </c>
       <c r="C29">
-        <v>181.9787335728203</v>
+        <v>180.4885444998721</v>
       </c>
       <c r="D29">
-        <v>231.8367335728203</v>
+        <v>232.7005444998721</v>
       </c>
       <c r="E29">
-        <v>-109.342</v>
+        <v>-106.988</v>
       </c>
       <c r="F29">
-        <v>63.55800000000001</v>
+        <v>65.91200000000001</v>
       </c>
       <c r="G29">
         <v>13.7</v>
@@ -3659,28 +3659,28 @@
         <v>16.929</v>
       </c>
       <c r="M29">
-        <v>3.514757400000001</v>
+        <v>3.6449336</v>
       </c>
       <c r="N29">
-        <v>13.4142426</v>
+        <v>13.2840664</v>
       </c>
       <c r="O29">
-        <v>3.621845502</v>
+        <v>3.586697928</v>
       </c>
       <c r="P29">
-        <v>9.792397097999999</v>
+        <v>9.697368471999999</v>
       </c>
       <c r="Q29">
-        <v>9.738397097999998</v>
+        <v>9.643368471999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1481420771120609</v>
+        <v>0.1492613036771534</v>
       </c>
       <c r="T29">
-        <v>1.226031712760146</v>
+        <v>1.239439758612728</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.816548647141335</v>
+        <v>4.644529052600573</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1187714586475505</v>
+        <v>0.1190288210032965</v>
       </c>
       <c r="C30">
-        <v>180.4885444998721</v>
+        <v>177.3167195028921</v>
       </c>
       <c r="D30">
-        <v>232.7005444998721</v>
+        <v>231.8827195028921</v>
       </c>
       <c r="E30">
-        <v>-106.988</v>
+        <v>-104.634</v>
       </c>
       <c r="F30">
-        <v>65.91200000000001</v>
+        <v>68.26600000000001</v>
       </c>
       <c r="G30">
         <v>13.7</v>
@@ -3741,45 +3741,45 @@
         <v>16.929</v>
       </c>
       <c r="M30">
-        <v>3.6449336</v>
+        <v>3.945774800000001</v>
       </c>
       <c r="N30">
-        <v>13.2840664</v>
+        <v>12.9832252</v>
       </c>
       <c r="O30">
-        <v>3.586697928</v>
+        <v>3.505470804</v>
       </c>
       <c r="P30">
-        <v>9.697368471999999</v>
+        <v>9.477754395999998</v>
       </c>
       <c r="Q30">
-        <v>9.643368471999999</v>
+        <v>9.423754395999998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1492613036771534</v>
+        <v>0.1504120577511218</v>
       </c>
       <c r="T30">
-        <v>1.239439758612728</v>
+        <v>1.253225495897778</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.644529052600573</v>
+        <v>4.290412113737458</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1190288210032965</v>
+        <v>0.1187751833590425</v>
       </c>
       <c r="C31">
-        <v>177.3167195028921</v>
+        <v>175.7686672787073</v>
       </c>
       <c r="D31">
-        <v>231.8827195028921</v>
+        <v>232.6886672787073</v>
       </c>
       <c r="E31">
-        <v>-104.634</v>
+        <v>-102.28</v>
       </c>
       <c r="F31">
-        <v>68.26599999999999</v>
+        <v>70.62</v>
       </c>
       <c r="G31">
         <v>13.7</v>
@@ -3823,28 +3823,28 @@
         <v>16.929</v>
       </c>
       <c r="M31">
-        <v>3.9457748</v>
+        <v>4.081836000000001</v>
       </c>
       <c r="N31">
-        <v>12.9832252</v>
+        <v>12.847164</v>
       </c>
       <c r="O31">
-        <v>3.505470804</v>
+        <v>3.46873428</v>
       </c>
       <c r="P31">
-        <v>9.477754396</v>
+        <v>9.378429719999998</v>
       </c>
       <c r="Q31">
-        <v>9.423754396</v>
+        <v>9.324429719999998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1504120577511218</v>
+        <v>0.1515956905129179</v>
       </c>
       <c r="T31">
-        <v>1.253225495897778</v>
+        <v>1.267405111390972</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.290412113737459</v>
+        <v>4.147398376612876</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1187751833590425</v>
+        <v>0.1185215457147885</v>
       </c>
       <c r="C32">
-        <v>175.7686672787073</v>
+        <v>174.2262370113507</v>
       </c>
       <c r="D32">
-        <v>232.6886672787073</v>
+        <v>233.5002370113507</v>
       </c>
       <c r="E32">
-        <v>-102.28</v>
+        <v>-99.926</v>
       </c>
       <c r="F32">
-        <v>70.62</v>
+        <v>72.974</v>
       </c>
       <c r="G32">
         <v>13.7</v>
@@ -3905,28 +3905,28 @@
         <v>16.929</v>
       </c>
       <c r="M32">
-        <v>4.081836000000001</v>
+        <v>4.2178972</v>
       </c>
       <c r="N32">
-        <v>12.847164</v>
+        <v>12.7111028</v>
       </c>
       <c r="O32">
-        <v>3.46873428</v>
+        <v>3.431997756</v>
       </c>
       <c r="P32">
-        <v>9.378429719999998</v>
+        <v>9.279105044</v>
       </c>
       <c r="Q32">
-        <v>9.324429719999998</v>
+        <v>9.225105043999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1515956905129179</v>
+        <v>0.152813631470708</v>
       </c>
       <c r="T32">
-        <v>1.267405111390972</v>
+        <v>1.281995730231794</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.147398376612876</v>
+        <v>4.013611332206009</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1185215457147885</v>
+        <v>0.1190855080705345</v>
       </c>
       <c r="C33">
-        <v>174.2262370113507</v>
+        <v>170.0753559198608</v>
       </c>
       <c r="D33">
-        <v>233.5002370113507</v>
+        <v>231.7033559198608</v>
       </c>
       <c r="E33">
-        <v>-99.926</v>
+        <v>-97.572</v>
       </c>
       <c r="F33">
-        <v>72.974</v>
+        <v>75.328</v>
       </c>
       <c r="G33">
         <v>13.7</v>
@@ -3987,45 +3987,45 @@
         <v>16.929</v>
       </c>
       <c r="M33">
-        <v>4.2178972</v>
+        <v>4.617606400000001</v>
       </c>
       <c r="N33">
-        <v>12.7111028</v>
+        <v>12.3113936</v>
       </c>
       <c r="O33">
-        <v>3.431997756</v>
+        <v>3.324076272</v>
       </c>
       <c r="P33">
-        <v>9.279105044</v>
+        <v>8.987317328</v>
       </c>
       <c r="Q33">
-        <v>9.225105043999999</v>
+        <v>8.933317327999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.152813631470708</v>
+        <v>0.1540673942213743</v>
       </c>
       <c r="T33">
-        <v>1.281995730231794</v>
+        <v>1.297015484920877</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.013611332206009</v>
+        <v>3.666185147352532</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1190855080705345</v>
+        <v>0.1188574204262805</v>
       </c>
       <c r="C34">
-        <v>170.0753559198608</v>
+        <v>168.4447413379216</v>
       </c>
       <c r="D34">
-        <v>231.7033559198608</v>
+        <v>232.4267413379216</v>
       </c>
       <c r="E34">
-        <v>-97.572</v>
+        <v>-95.218</v>
       </c>
       <c r="F34">
-        <v>75.328</v>
+        <v>77.682</v>
       </c>
       <c r="G34">
         <v>13.7</v>
@@ -4069,28 +4069,28 @@
         <v>16.929</v>
       </c>
       <c r="M34">
-        <v>4.617606400000001</v>
+        <v>4.761906600000001</v>
       </c>
       <c r="N34">
-        <v>12.3113936</v>
+        <v>12.1670934</v>
       </c>
       <c r="O34">
-        <v>3.324076272</v>
+        <v>3.285115218</v>
       </c>
       <c r="P34">
-        <v>8.987317328</v>
+        <v>8.881978181999999</v>
       </c>
       <c r="Q34">
-        <v>8.933317327999999</v>
+        <v>8.827978181999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1540673942213743</v>
+        <v>0.1553585827257918</v>
       </c>
       <c r="T34">
-        <v>1.297015484920877</v>
+        <v>1.3124835904962</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.666185147352532</v>
+        <v>3.555088627735789</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1188574204262805</v>
+        <v>0.1193242927820265</v>
       </c>
       <c r="C35">
-        <v>168.4447413379216</v>
+        <v>164.6148533536807</v>
       </c>
       <c r="D35">
-        <v>232.4267413379216</v>
+        <v>230.9508533536807</v>
       </c>
       <c r="E35">
-        <v>-95.218</v>
+        <v>-92.864</v>
       </c>
       <c r="F35">
-        <v>77.682</v>
+        <v>80.036</v>
       </c>
       <c r="G35">
         <v>13.7</v>
@@ -4151,45 +4151,45 @@
         <v>16.929</v>
       </c>
       <c r="M35">
-        <v>4.761906600000001</v>
+        <v>5.1303076</v>
       </c>
       <c r="N35">
-        <v>12.1670934</v>
+        <v>11.7986924</v>
       </c>
       <c r="O35">
-        <v>3.285115218</v>
+        <v>3.185646948</v>
       </c>
       <c r="P35">
-        <v>8.881978181999999</v>
+        <v>8.613045451999998</v>
       </c>
       <c r="Q35">
-        <v>8.827978181999999</v>
+        <v>8.559045451999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1553585827257918</v>
+        <v>0.1566888981545857</v>
       </c>
       <c r="T35">
-        <v>1.3124835904962</v>
+        <v>1.328420426543503</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.555088627735789</v>
+        <v>3.299802140518826</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1193242927820265</v>
+        <v>0.1191166451377726</v>
       </c>
       <c r="C36">
-        <v>164.6148533536807</v>
+        <v>162.9149531225287</v>
       </c>
       <c r="D36">
-        <v>230.9508533536807</v>
+        <v>231.6049531225288</v>
       </c>
       <c r="E36">
-        <v>-92.864</v>
+        <v>-90.50999999999999</v>
       </c>
       <c r="F36">
-        <v>80.036</v>
+        <v>82.39000000000001</v>
       </c>
       <c r="G36">
         <v>13.7</v>
@@ -4233,28 +4233,28 @@
         <v>16.929</v>
       </c>
       <c r="M36">
-        <v>5.1303076</v>
+        <v>5.281199000000001</v>
       </c>
       <c r="N36">
-        <v>11.7986924</v>
+        <v>11.647801</v>
       </c>
       <c r="O36">
-        <v>3.185646948</v>
+        <v>3.144906269999999</v>
       </c>
       <c r="P36">
-        <v>8.613045451999998</v>
+        <v>8.502894729999998</v>
       </c>
       <c r="Q36">
-        <v>8.559045451999998</v>
+        <v>8.448894729999997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1566888981545857</v>
+        <v>0.158060146365804</v>
       </c>
       <c r="T36">
-        <v>1.328420426543503</v>
+        <v>1.344847626776877</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.299802140518826</v>
+        <v>3.205522079361144</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1191166451377726</v>
+        <v>0.1189089974935186</v>
       </c>
       <c r="C37">
-        <v>162.9149531225287</v>
+        <v>161.2187685017878</v>
       </c>
       <c r="D37">
-        <v>231.6049531225288</v>
+        <v>232.2627685017879</v>
       </c>
       <c r="E37">
-        <v>-90.50999999999999</v>
+        <v>-88.15599999999999</v>
       </c>
       <c r="F37">
-        <v>82.39000000000001</v>
+        <v>84.74400000000001</v>
       </c>
       <c r="G37">
         <v>13.7</v>
@@ -4315,28 +4315,28 @@
         <v>16.929</v>
       </c>
       <c r="M37">
-        <v>5.281199000000001</v>
+        <v>5.432090400000002</v>
       </c>
       <c r="N37">
-        <v>11.647801</v>
+        <v>11.4969096</v>
       </c>
       <c r="O37">
-        <v>3.144906269999999</v>
+        <v>3.104165591999999</v>
       </c>
       <c r="P37">
-        <v>8.502894729999998</v>
+        <v>8.392744007999998</v>
       </c>
       <c r="Q37">
-        <v>8.448894729999997</v>
+        <v>8.338744007999997</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.158060146365804</v>
+        <v>0.1594742460836228</v>
       </c>
       <c r="T37">
-        <v>1.344847626776877</v>
+        <v>1.361788177017544</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.205522079361144</v>
+        <v>3.11647979937889</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1189089974935186</v>
+        <v>0.1187013498492646</v>
       </c>
       <c r="C38">
-        <v>161.2187685017878</v>
+        <v>159.5263312413946</v>
       </c>
       <c r="D38">
-        <v>232.2627685017878</v>
+        <v>232.9243312413946</v>
       </c>
       <c r="E38">
-        <v>-88.15600000000001</v>
+        <v>-85.80200000000001</v>
       </c>
       <c r="F38">
-        <v>84.744</v>
+        <v>87.098</v>
       </c>
       <c r="G38">
         <v>13.7</v>
@@ -4397,28 +4397,28 @@
         <v>16.929</v>
       </c>
       <c r="M38">
-        <v>5.432090400000001</v>
+        <v>5.582981800000001</v>
       </c>
       <c r="N38">
-        <v>11.4969096</v>
+        <v>11.3460182</v>
       </c>
       <c r="O38">
-        <v>3.104165592</v>
+        <v>3.063424914</v>
       </c>
       <c r="P38">
-        <v>8.392744007999999</v>
+        <v>8.282593285999997</v>
       </c>
       <c r="Q38">
-        <v>8.338744007999999</v>
+        <v>8.228593285999997</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1594742460836228</v>
+        <v>0.1609332378559755</v>
       </c>
       <c r="T38">
-        <v>1.361788177017544</v>
+        <v>1.379266522503946</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.116479799378891</v>
+        <v>3.032250615611893</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1187013498492646</v>
+        <v>0.1206574222050106</v>
       </c>
       <c r="C39">
-        <v>159.5263312413946</v>
+        <v>151.0858693796151</v>
       </c>
       <c r="D39">
-        <v>232.9243312413946</v>
+        <v>226.8378693796151</v>
       </c>
       <c r="E39">
-        <v>-85.80200000000001</v>
+        <v>-83.44800000000001</v>
       </c>
       <c r="F39">
-        <v>87.098</v>
+        <v>89.452</v>
       </c>
       <c r="G39">
         <v>13.7</v>
@@ -4479,45 +4479,45 @@
         <v>16.929</v>
       </c>
       <c r="M39">
-        <v>5.582981800000001</v>
+        <v>6.431598800000001</v>
       </c>
       <c r="N39">
-        <v>11.3460182</v>
+        <v>10.4974012</v>
       </c>
       <c r="O39">
-        <v>3.063424914</v>
+        <v>2.834298324</v>
       </c>
       <c r="P39">
-        <v>8.282593285999997</v>
+        <v>7.663102875999999</v>
       </c>
       <c r="Q39">
-        <v>8.228593285999997</v>
+        <v>7.609102875999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1609332378559755</v>
+        <v>0.1624392938790493</v>
       </c>
       <c r="T39">
-        <v>1.379266522503946</v>
+        <v>1.397308685586683</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.27</v>
       </c>
       <c r="W39">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.032250615611893</v>
+        <v>2.632160451301782</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1206574222050106</v>
+        <v>0.1205067145607566</v>
       </c>
       <c r="C40">
-        <v>151.0858693796151</v>
+        <v>149.1894748455065</v>
       </c>
       <c r="D40">
-        <v>226.8378693796151</v>
+        <v>227.2954748455065</v>
       </c>
       <c r="E40">
-        <v>-83.44800000000001</v>
+        <v>-81.09399999999999</v>
       </c>
       <c r="F40">
-        <v>89.452</v>
+        <v>91.80600000000001</v>
       </c>
       <c r="G40">
         <v>13.7</v>
@@ -4561,28 +4561,28 @@
         <v>16.929</v>
       </c>
       <c r="M40">
-        <v>6.431598800000001</v>
+        <v>6.600851400000002</v>
       </c>
       <c r="N40">
-        <v>10.4974012</v>
+        <v>10.3281486</v>
       </c>
       <c r="O40">
-        <v>2.834298324</v>
+        <v>2.788600121999999</v>
       </c>
       <c r="P40">
-        <v>7.663102875999999</v>
+        <v>7.539548477999998</v>
       </c>
       <c r="Q40">
-        <v>7.609102875999999</v>
+        <v>7.485548477999997</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1624392938790493</v>
+        <v>0.1639947287881256</v>
       </c>
       <c r="T40">
-        <v>1.397308685586683</v>
+        <v>1.415942395000003</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.632160451301782</v>
+        <v>2.564669157678659</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1205067145607566</v>
+        <v>0.1203560069165026</v>
       </c>
       <c r="C41">
-        <v>149.1894748455065</v>
+        <v>147.2949303203943</v>
       </c>
       <c r="D41">
-        <v>227.2954748455065</v>
+        <v>227.7549303203943</v>
       </c>
       <c r="E41">
-        <v>-81.09399999999999</v>
+        <v>-78.73999999999999</v>
       </c>
       <c r="F41">
-        <v>91.80600000000001</v>
+        <v>94.16000000000001</v>
       </c>
       <c r="G41">
         <v>13.7</v>
@@ -4643,28 +4643,28 @@
         <v>16.929</v>
       </c>
       <c r="M41">
-        <v>6.600851400000002</v>
+        <v>6.770104000000002</v>
       </c>
       <c r="N41">
-        <v>10.3281486</v>
+        <v>10.158896</v>
       </c>
       <c r="O41">
-        <v>2.788600121999999</v>
+        <v>2.742901919999999</v>
       </c>
       <c r="P41">
-        <v>7.539548477999998</v>
+        <v>7.415994079999997</v>
       </c>
       <c r="Q41">
-        <v>7.485548477999997</v>
+        <v>7.361994079999997</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1639947287881256</v>
+        <v>0.1656020115275044</v>
       </c>
       <c r="T41">
-        <v>1.415942395000003</v>
+        <v>1.435197228060433</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.564669157678659</v>
+        <v>2.500552428736692</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1203560069165026</v>
+        <v>0.1213725692722486</v>
       </c>
       <c r="C42">
-        <v>147.2949303203943</v>
+        <v>141.8772910829192</v>
       </c>
       <c r="D42">
-        <v>227.7549303203943</v>
+        <v>224.6912910829192</v>
       </c>
       <c r="E42">
-        <v>-78.73999999999999</v>
+        <v>-76.386</v>
       </c>
       <c r="F42">
-        <v>94.16000000000001</v>
+        <v>96.51400000000001</v>
       </c>
       <c r="G42">
         <v>13.7</v>
@@ -4725,45 +4725,45 @@
         <v>16.929</v>
       </c>
       <c r="M42">
-        <v>6.770104000000002</v>
+        <v>7.315761200000002</v>
       </c>
       <c r="N42">
-        <v>10.158896</v>
+        <v>9.613238799999998</v>
       </c>
       <c r="O42">
-        <v>2.742901919999999</v>
+        <v>2.595574475999999</v>
       </c>
       <c r="P42">
-        <v>7.415994079999997</v>
+        <v>7.017664323999998</v>
       </c>
       <c r="Q42">
-        <v>7.361994079999997</v>
+        <v>6.963664323999998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1656020115275044</v>
+        <v>0.1672637784275401</v>
       </c>
       <c r="T42">
-        <v>1.435197228060433</v>
+        <v>1.455104767326301</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.500552428736692</v>
+        <v>2.314044914423942</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1213725692722486</v>
+        <v>0.1212503316279947</v>
       </c>
       <c r="C43">
-        <v>141.8772910829192</v>
+        <v>139.8873151171909</v>
       </c>
       <c r="D43">
-        <v>224.6912910829192</v>
+        <v>225.0553151171909</v>
       </c>
       <c r="E43">
-        <v>-76.386</v>
+        <v>-74.032</v>
       </c>
       <c r="F43">
-        <v>96.51400000000001</v>
+        <v>98.86800000000001</v>
       </c>
       <c r="G43">
         <v>13.7</v>
@@ -4807,28 +4807,28 @@
         <v>16.929</v>
       </c>
       <c r="M43">
-        <v>7.315761200000002</v>
+        <v>7.494194400000001</v>
       </c>
       <c r="N43">
-        <v>9.613238799999998</v>
+        <v>9.434805599999997</v>
       </c>
       <c r="O43">
-        <v>2.595574475999999</v>
+        <v>2.547397511999999</v>
       </c>
       <c r="P43">
-        <v>7.017664323999998</v>
+        <v>6.887408087999997</v>
       </c>
       <c r="Q43">
-        <v>6.963664323999998</v>
+        <v>6.833408087999997</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1672637784275401</v>
+        <v>0.1689828476344735</v>
       </c>
       <c r="T43">
-        <v>1.455104767326301</v>
+        <v>1.475698773463407</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.314044914423942</v>
+        <v>2.258948606937658</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1212503316279947</v>
+        <v>0.1211280939837407</v>
       </c>
       <c r="C44">
-        <v>139.8873151171909</v>
+        <v>137.8985205816051</v>
       </c>
       <c r="D44">
-        <v>225.0553151171909</v>
+        <v>225.420520581605</v>
       </c>
       <c r="E44">
-        <v>-74.03200000000001</v>
+        <v>-71.67800000000001</v>
       </c>
       <c r="F44">
-        <v>98.86799999999999</v>
+        <v>101.222</v>
       </c>
       <c r="G44">
         <v>13.7</v>
@@ -4889,28 +4889,28 @@
         <v>16.929</v>
       </c>
       <c r="M44">
-        <v>7.4941944</v>
+        <v>7.6726276</v>
       </c>
       <c r="N44">
-        <v>9.434805599999997</v>
+        <v>9.256372399999998</v>
       </c>
       <c r="O44">
-        <v>2.547397511999999</v>
+        <v>2.499220548</v>
       </c>
       <c r="P44">
-        <v>6.887408087999997</v>
+        <v>6.757151851999998</v>
       </c>
       <c r="Q44">
-        <v>6.833408087999997</v>
+        <v>6.703151851999998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1689828476344735</v>
+        <v>0.1707622350591941</v>
       </c>
       <c r="T44">
-        <v>1.475698773463406</v>
+        <v>1.497015376307077</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.258948606937658</v>
+        <v>2.206414918404224</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1211280939837407</v>
+        <v>0.1210058563394867</v>
       </c>
       <c r="C45">
-        <v>137.8985205816051</v>
+        <v>135.9109132369592</v>
       </c>
       <c r="D45">
-        <v>225.420520581605</v>
+        <v>225.7869132369592</v>
       </c>
       <c r="E45">
-        <v>-71.67800000000001</v>
+        <v>-69.324</v>
       </c>
       <c r="F45">
-        <v>101.222</v>
+        <v>103.576</v>
       </c>
       <c r="G45">
         <v>13.7</v>
@@ -4971,28 +4971,28 @@
         <v>16.929</v>
       </c>
       <c r="M45">
-        <v>7.6726276</v>
+        <v>7.851060800000001</v>
       </c>
       <c r="N45">
-        <v>9.256372399999998</v>
+        <v>9.077939199999998</v>
       </c>
       <c r="O45">
-        <v>2.499220548</v>
+        <v>2.451043583999999</v>
       </c>
       <c r="P45">
-        <v>6.757151851999998</v>
+        <v>6.626895615999999</v>
       </c>
       <c r="Q45">
-        <v>6.703151851999998</v>
+        <v>6.572895615999998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1707622350591941</v>
+        <v>0.1726051720347976</v>
       </c>
       <c r="T45">
-        <v>1.497015376307077</v>
+        <v>1.519093286395163</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.206414918404224</v>
+        <v>2.156269124804128</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1210058563394867</v>
+        <v>0.1208836186952327</v>
       </c>
       <c r="C46">
-        <v>135.9109132369592</v>
+        <v>133.9244988815655</v>
       </c>
       <c r="D46">
-        <v>225.7869132369592</v>
+        <v>226.1544988815655</v>
       </c>
       <c r="E46">
-        <v>-69.324</v>
+        <v>-66.97</v>
       </c>
       <c r="F46">
-        <v>103.576</v>
+        <v>105.93</v>
       </c>
       <c r="G46">
         <v>13.7</v>
@@ -5053,28 +5053,28 @@
         <v>16.929</v>
       </c>
       <c r="M46">
-        <v>7.851060800000001</v>
+        <v>8.029494000000001</v>
       </c>
       <c r="N46">
-        <v>9.077939199999998</v>
+        <v>8.899505999999997</v>
       </c>
       <c r="O46">
-        <v>2.451043583999999</v>
+        <v>2.402866619999999</v>
       </c>
       <c r="P46">
-        <v>6.626895615999999</v>
+        <v>6.496639379999998</v>
       </c>
       <c r="Q46">
-        <v>6.572895615999998</v>
+        <v>6.442639379999997</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1726051720347976</v>
+        <v>0.1745151249004231</v>
       </c>
       <c r="T46">
-        <v>1.519093286395163</v>
+        <v>1.541974029577363</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.156269124804128</v>
+        <v>2.108352033141814</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1208836186952327</v>
+        <v>0.1207613810509787</v>
       </c>
       <c r="C47">
-        <v>133.9244988815655</v>
+        <v>131.9392833515571</v>
       </c>
       <c r="D47">
-        <v>226.1544988815655</v>
+        <v>226.5232833515571</v>
       </c>
       <c r="E47">
-        <v>-66.97</v>
+        <v>-64.616</v>
       </c>
       <c r="F47">
-        <v>105.93</v>
+        <v>108.284</v>
       </c>
       <c r="G47">
         <v>13.7</v>
@@ -5135,28 +5135,28 @@
         <v>16.929</v>
       </c>
       <c r="M47">
-        <v>8.029494000000001</v>
+        <v>8.2079272</v>
       </c>
       <c r="N47">
-        <v>8.899505999999997</v>
+        <v>8.721072799999998</v>
       </c>
       <c r="O47">
-        <v>2.402866619999999</v>
+        <v>2.354689656</v>
       </c>
       <c r="P47">
-        <v>6.496639379999998</v>
+        <v>6.366383143999998</v>
       </c>
       <c r="Q47">
-        <v>6.442639379999997</v>
+        <v>6.312383143999998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1745151249004231</v>
+        <v>0.1764958167610717</v>
       </c>
       <c r="T47">
-        <v>1.541974029577363</v>
+        <v>1.565702207692236</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.108352033141814</v>
+        <v>2.062518293290905</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1207613810509787</v>
+        <v>0.1206391434067247</v>
       </c>
       <c r="C48">
-        <v>131.9392833515571</v>
+        <v>129.9552725211964</v>
       </c>
       <c r="D48">
-        <v>226.5232833515571</v>
+        <v>226.8932725211965</v>
       </c>
       <c r="E48">
-        <v>-64.616</v>
+        <v>-62.262</v>
       </c>
       <c r="F48">
-        <v>108.284</v>
+        <v>110.638</v>
       </c>
       <c r="G48">
         <v>13.7</v>
@@ -5217,28 +5217,28 @@
         <v>16.929</v>
       </c>
       <c r="M48">
-        <v>8.2079272</v>
+        <v>8.386360400000001</v>
       </c>
       <c r="N48">
-        <v>8.721072799999998</v>
+        <v>8.542639599999998</v>
       </c>
       <c r="O48">
-        <v>2.354689656</v>
+        <v>2.306512692</v>
       </c>
       <c r="P48">
-        <v>6.366383143999998</v>
+        <v>6.236126907999997</v>
       </c>
       <c r="Q48">
-        <v>6.312383143999998</v>
+        <v>6.182126907999997</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1764958167610717</v>
+        <v>0.1785512517108013</v>
       </c>
       <c r="T48">
-        <v>1.565702207692236</v>
+        <v>1.59032578875484</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.062518293290905</v>
+        <v>2.018634925348545</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1206391434067247</v>
+        <v>0.1254925857624707</v>
       </c>
       <c r="C49">
-        <v>129.9552725211964</v>
+        <v>113.7830056328507</v>
       </c>
       <c r="D49">
-        <v>226.8932725211965</v>
+        <v>213.0750056328508</v>
       </c>
       <c r="E49">
-        <v>-62.262</v>
+        <v>-59.90799999999999</v>
       </c>
       <c r="F49">
-        <v>110.638</v>
+        <v>112.992</v>
       </c>
       <c r="G49">
         <v>13.7</v>
@@ -5299,45 +5299,45 @@
         <v>16.929</v>
       </c>
       <c r="M49">
-        <v>8.386360400000001</v>
+        <v>10.16928</v>
       </c>
       <c r="N49">
-        <v>8.542639599999998</v>
+        <v>6.759719999999998</v>
       </c>
       <c r="O49">
-        <v>2.306512692</v>
+        <v>1.8251244</v>
       </c>
       <c r="P49">
-        <v>6.236126907999997</v>
+        <v>4.934595599999998</v>
       </c>
       <c r="Q49">
-        <v>6.182126907999997</v>
+        <v>4.880595599999998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1785512517108013</v>
+        <v>0.1806857418509052</v>
       </c>
       <c r="T49">
-        <v>1.59032578875484</v>
+        <v>1.615896430627545</v>
       </c>
       <c r="U49">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.018634925348545</v>
+        <v>1.664719626168224</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1254925857624707</v>
+        <v>0.1254740081182167</v>
       </c>
       <c r="C50">
-        <v>113.7830056328508</v>
+        <v>111.4786884810914</v>
       </c>
       <c r="D50">
-        <v>213.0750056328508</v>
+        <v>213.1246884810914</v>
       </c>
       <c r="E50">
-        <v>-59.908</v>
+        <v>-57.554</v>
       </c>
       <c r="F50">
-        <v>112.992</v>
+        <v>115.346</v>
       </c>
       <c r="G50">
         <v>13.7</v>
@@ -5381,28 +5381,28 @@
         <v>16.929</v>
       </c>
       <c r="M50">
-        <v>10.16928</v>
+        <v>10.38114</v>
       </c>
       <c r="N50">
-        <v>6.759719999999998</v>
+        <v>6.547859999999998</v>
       </c>
       <c r="O50">
-        <v>1.8251244</v>
+        <v>1.7679222</v>
       </c>
       <c r="P50">
-        <v>4.934595599999998</v>
+        <v>4.779937799999999</v>
       </c>
       <c r="Q50">
-        <v>4.880595599999998</v>
+        <v>4.725937799999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1806857418509052</v>
+        <v>0.1829039374866995</v>
       </c>
       <c r="T50">
-        <v>1.615896430627545</v>
+        <v>1.642469842769767</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.664719626168224</v>
+        <v>1.630745756246424</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1254740081182167</v>
+        <v>0.1254554304739627</v>
       </c>
       <c r="C51">
-        <v>111.4786884810914</v>
+        <v>109.1743945039048</v>
       </c>
       <c r="D51">
-        <v>213.1246884810914</v>
+        <v>213.1743945039048</v>
       </c>
       <c r="E51">
-        <v>-57.554</v>
+        <v>-55.2</v>
       </c>
       <c r="F51">
-        <v>115.346</v>
+        <v>117.7</v>
       </c>
       <c r="G51">
         <v>13.7</v>
@@ -5463,28 +5463,28 @@
         <v>16.929</v>
       </c>
       <c r="M51">
-        <v>10.38114</v>
+        <v>10.593</v>
       </c>
       <c r="N51">
-        <v>6.547859999999998</v>
+        <v>6.335999999999999</v>
       </c>
       <c r="O51">
-        <v>1.7679222</v>
+        <v>1.71072</v>
       </c>
       <c r="P51">
-        <v>4.779937799999999</v>
+        <v>4.625279999999998</v>
       </c>
       <c r="Q51">
-        <v>4.725937799999999</v>
+        <v>4.571279999999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1829039374866995</v>
+        <v>0.1852108609479255</v>
       </c>
       <c r="T51">
-        <v>1.642469842769767</v>
+        <v>1.670106191397679</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.630745756246424</v>
+        <v>1.598130841121495</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1254554304739627</v>
+        <v>0.1254368528297087</v>
       </c>
       <c r="C52">
-        <v>109.1743945039048</v>
+        <v>106.8701237175092</v>
       </c>
       <c r="D52">
-        <v>213.1743945039048</v>
+        <v>213.2241237175093</v>
       </c>
       <c r="E52">
-        <v>-55.2</v>
+        <v>-52.846</v>
       </c>
       <c r="F52">
-        <v>117.7</v>
+        <v>120.054</v>
       </c>
       <c r="G52">
         <v>13.7</v>
@@ -5545,28 +5545,28 @@
         <v>16.929</v>
       </c>
       <c r="M52">
-        <v>10.593</v>
+        <v>10.80486</v>
       </c>
       <c r="N52">
-        <v>6.335999999999999</v>
+        <v>6.124139999999999</v>
       </c>
       <c r="O52">
-        <v>1.71072</v>
+        <v>1.6535178</v>
       </c>
       <c r="P52">
-        <v>4.625279999999998</v>
+        <v>4.470622199999999</v>
       </c>
       <c r="Q52">
-        <v>4.571279999999998</v>
+        <v>4.416622199999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1852108609479255</v>
+        <v>0.187611944550426</v>
       </c>
       <c r="T52">
-        <v>1.670106191397679</v>
+        <v>1.698870554255301</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.598130841121495</v>
+        <v>1.566794942275976</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1254368528297087</v>
+        <v>0.1254182751854548</v>
       </c>
       <c r="C53">
-        <v>106.8701237175092</v>
+        <v>104.5658761381383</v>
       </c>
       <c r="D53">
-        <v>213.2241237175093</v>
+        <v>213.2738761381383</v>
       </c>
       <c r="E53">
-        <v>-52.846</v>
+        <v>-50.492</v>
       </c>
       <c r="F53">
-        <v>120.054</v>
+        <v>122.408</v>
       </c>
       <c r="G53">
         <v>13.7</v>
@@ -5627,28 +5627,28 @@
         <v>16.929</v>
       </c>
       <c r="M53">
-        <v>10.80486</v>
+        <v>11.01672</v>
       </c>
       <c r="N53">
-        <v>6.124139999999999</v>
+        <v>5.912279999999999</v>
       </c>
       <c r="O53">
-        <v>1.6535178</v>
+        <v>1.5963156</v>
       </c>
       <c r="P53">
-        <v>4.470622199999999</v>
+        <v>4.315964399999999</v>
       </c>
       <c r="Q53">
-        <v>4.416622199999999</v>
+        <v>4.261964399999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.187611944550426</v>
+        <v>0.1901130733030308</v>
       </c>
       <c r="T53">
-        <v>1.698870554255301</v>
+        <v>1.72883343223199</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.566794942275976</v>
+        <v>1.53666427030913</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1254182751854548</v>
+        <v>0.1253996975412008</v>
       </c>
       <c r="C54">
-        <v>104.5658761381383</v>
+        <v>102.2616517820409</v>
       </c>
       <c r="D54">
-        <v>213.2738761381383</v>
+        <v>213.3236517820409</v>
       </c>
       <c r="E54">
-        <v>-50.492</v>
+        <v>-48.13799999999999</v>
       </c>
       <c r="F54">
-        <v>122.408</v>
+        <v>124.762</v>
       </c>
       <c r="G54">
         <v>13.7</v>
@@ -5709,28 +5709,28 @@
         <v>16.929</v>
       </c>
       <c r="M54">
-        <v>11.01672</v>
+        <v>11.22858</v>
       </c>
       <c r="N54">
-        <v>5.912279999999999</v>
+        <v>5.700419999999998</v>
       </c>
       <c r="O54">
-        <v>1.5963156</v>
+        <v>1.5391134</v>
       </c>
       <c r="P54">
-        <v>4.315964399999999</v>
+        <v>4.161306599999998</v>
       </c>
       <c r="Q54">
-        <v>4.261964399999999</v>
+        <v>4.107306599999998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1901130733030308</v>
+        <v>0.1927206330663847</v>
       </c>
       <c r="T54">
-        <v>1.72883343223199</v>
+        <v>1.760071326292794</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.53666427030913</v>
+        <v>1.507670604831599</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1253996975412008</v>
+        <v>0.1508481064391486</v>
       </c>
       <c r="C55">
-        <v>102.2616517820409</v>
+        <v>48.22897139290382</v>
       </c>
       <c r="D55">
-        <v>213.3236517820409</v>
+        <v>161.6449713929038</v>
       </c>
       <c r="E55">
-        <v>-48.13799999999999</v>
+        <v>-45.78399999999999</v>
       </c>
       <c r="F55">
-        <v>124.762</v>
+        <v>127.116</v>
       </c>
       <c r="G55">
         <v>13.7</v>
@@ -5791,45 +5791,45 @@
         <v>16.929</v>
       </c>
       <c r="M55">
-        <v>11.22858</v>
+        <v>18.6606288</v>
       </c>
       <c r="N55">
-        <v>5.700419999999998</v>
+        <v>-1.731628800000006</v>
       </c>
       <c r="O55">
-        <v>1.5391134</v>
+        <v>-0.4675397760000017</v>
       </c>
       <c r="P55">
-        <v>4.161306599999998</v>
+        <v>-1.264089024000005</v>
       </c>
       <c r="Q55">
-        <v>4.107306599999998</v>
+        <v>-1.318089024000005</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1927206330663847</v>
+        <v>0.1978117307799451</v>
       </c>
       <c r="T55">
-        <v>1.760071326292794</v>
+        <v>1.821061365050276</v>
       </c>
       <c r="U55">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.27</v>
+        <v>0.2449451221064962</v>
       </c>
       <c r="W55">
-        <v>0.06569999999999999</v>
+        <v>0.1108420560747664</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.507670604831599</v>
+        <v>0.9072041559499857</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1508481064391486</v>
+        <v>0.1518581064391486</v>
       </c>
       <c r="C56">
-        <v>48.22897139290382</v>
+        <v>44.33561314308901</v>
       </c>
       <c r="D56">
-        <v>161.6449713929038</v>
+        <v>160.105613143089</v>
       </c>
       <c r="E56">
-        <v>-45.78399999999999</v>
+        <v>-43.42999999999998</v>
       </c>
       <c r="F56">
-        <v>127.116</v>
+        <v>129.47</v>
       </c>
       <c r="G56">
         <v>13.7</v>
@@ -5873,37 +5873,37 @@
         <v>16.929</v>
       </c>
       <c r="M56">
-        <v>18.6606288</v>
+        <v>19.00619600000001</v>
       </c>
       <c r="N56">
-        <v>-1.731628800000006</v>
+        <v>-2.077196000000008</v>
       </c>
       <c r="O56">
-        <v>-0.4675397760000017</v>
+        <v>-0.5608429200000021</v>
       </c>
       <c r="P56">
-        <v>-1.264089024000005</v>
+        <v>-1.516353080000006</v>
       </c>
       <c r="Q56">
-        <v>-1.318089024000005</v>
+        <v>-1.570353080000006</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1978117307799451</v>
+        <v>0.2011897692417217</v>
       </c>
       <c r="T56">
-        <v>1.821061365050276</v>
+        <v>1.861529395384727</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2449451221064962</v>
+        <v>0.2404915744318326</v>
       </c>
       <c r="W56">
-        <v>0.1108420560747664</v>
+        <v>0.111495836873407</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9072041559499857</v>
+        <v>0.8907095349327131</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1518581064391486</v>
+        <v>0.1528681064391486</v>
       </c>
       <c r="C57">
-        <v>44.33561314308901</v>
+        <v>40.47129718951024</v>
       </c>
       <c r="D57">
-        <v>160.105613143089</v>
+        <v>158.5952971895103</v>
       </c>
       <c r="E57">
-        <v>-43.42999999999998</v>
+        <v>-41.07599999999999</v>
       </c>
       <c r="F57">
-        <v>129.47</v>
+        <v>131.824</v>
       </c>
       <c r="G57">
         <v>13.7</v>
@@ -5955,37 +5955,37 @@
         <v>16.929</v>
       </c>
       <c r="M57">
-        <v>19.00619600000001</v>
+        <v>19.3517632</v>
       </c>
       <c r="N57">
-        <v>-2.077196000000008</v>
+        <v>-2.422763200000006</v>
       </c>
       <c r="O57">
-        <v>-0.5608429200000021</v>
+        <v>-0.6541460640000015</v>
       </c>
       <c r="P57">
-        <v>-1.516353080000006</v>
+        <v>-1.768617136000004</v>
       </c>
       <c r="Q57">
-        <v>-1.570353080000006</v>
+        <v>-1.822617136000004</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2011897692417217</v>
+        <v>0.2047213549063063</v>
       </c>
       <c r="T57">
-        <v>1.861529395384727</v>
+        <v>1.903836881643471</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2404915744318326</v>
+        <v>0.2361970820312642</v>
       </c>
       <c r="W57">
-        <v>0.111495836873407</v>
+        <v>0.1121262683578104</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8907095349327131</v>
+        <v>0.8748040075232005</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1528681064391486</v>
+        <v>0.1538781064391486</v>
       </c>
       <c r="C58">
-        <v>40.47129718951024</v>
+        <v>36.63520932325406</v>
       </c>
       <c r="D58">
-        <v>158.5952971895103</v>
+        <v>157.1132093232541</v>
       </c>
       <c r="E58">
-        <v>-41.07599999999999</v>
+        <v>-38.72199999999998</v>
       </c>
       <c r="F58">
-        <v>131.824</v>
+        <v>134.178</v>
       </c>
       <c r="G58">
         <v>13.7</v>
@@ -6037,37 +6037,37 @@
         <v>16.929</v>
       </c>
       <c r="M58">
-        <v>19.3517632</v>
+        <v>19.69733040000001</v>
       </c>
       <c r="N58">
-        <v>-2.422763200000006</v>
+        <v>-2.768330400000007</v>
       </c>
       <c r="O58">
-        <v>-0.6541460640000015</v>
+        <v>-0.7474492080000019</v>
       </c>
       <c r="P58">
-        <v>-1.768617136000004</v>
+        <v>-2.020881192000005</v>
       </c>
       <c r="Q58">
-        <v>-1.822617136000004</v>
+        <v>-2.074881192000005</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2047213549063063</v>
+        <v>0.2084172003692437</v>
       </c>
       <c r="T58">
-        <v>1.903836881643471</v>
+        <v>1.948112157960761</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2361970820312642</v>
+        <v>0.2320532735745753</v>
       </c>
       <c r="W58">
-        <v>0.1121262683578104</v>
+        <v>0.1127345794392524</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8748040075232005</v>
+        <v>0.8594565687947233</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1538781064391486</v>
+        <v>0.1548881064391486</v>
       </c>
       <c r="C59">
-        <v>36.63520932325406</v>
+        <v>32.826565489052</v>
       </c>
       <c r="D59">
-        <v>157.1132093232541</v>
+        <v>155.658565489052</v>
       </c>
       <c r="E59">
-        <v>-38.72199999999998</v>
+        <v>-36.36799999999999</v>
       </c>
       <c r="F59">
-        <v>134.178</v>
+        <v>136.532</v>
       </c>
       <c r="G59">
         <v>13.7</v>
@@ -6119,37 +6119,37 @@
         <v>16.929</v>
       </c>
       <c r="M59">
-        <v>19.69733040000001</v>
+        <v>20.0428976</v>
       </c>
       <c r="N59">
-        <v>-2.768330400000007</v>
+        <v>-3.113897600000005</v>
       </c>
       <c r="O59">
-        <v>-0.7474492080000019</v>
+        <v>-0.8407523520000014</v>
       </c>
       <c r="P59">
-        <v>-2.020881192000005</v>
+        <v>-2.273145248000004</v>
       </c>
       <c r="Q59">
-        <v>-2.074881192000005</v>
+        <v>-2.327145248000003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2084172003692437</v>
+        <v>0.2122890384732733</v>
       </c>
       <c r="T59">
-        <v>1.948112157960761</v>
+        <v>1.994495780769351</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2320532735745753</v>
+        <v>0.2280523550646689</v>
       </c>
       <c r="W59">
-        <v>0.1127345794392524</v>
+        <v>0.1133219142765066</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8594565687947233</v>
+        <v>0.8446383520913661</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1548881064391486</v>
+        <v>0.1558981064391486</v>
       </c>
       <c r="C60">
-        <v>32.82656548905203</v>
+        <v>29.04461040218743</v>
       </c>
       <c r="D60">
-        <v>155.658565489052</v>
+        <v>154.2306104021874</v>
       </c>
       <c r="E60">
-        <v>-36.36800000000002</v>
+        <v>-34.01400000000001</v>
       </c>
       <c r="F60">
-        <v>136.532</v>
+        <v>138.886</v>
       </c>
       <c r="G60">
         <v>13.7</v>
@@ -6201,37 +6201,37 @@
         <v>16.929</v>
       </c>
       <c r="M60">
-        <v>20.0428976</v>
+        <v>20.3884648</v>
       </c>
       <c r="N60">
-        <v>-3.113897600000001</v>
+        <v>-3.459464800000003</v>
       </c>
       <c r="O60">
-        <v>-0.8407523520000004</v>
+        <v>-0.9340554960000008</v>
       </c>
       <c r="P60">
-        <v>-2.273145248000001</v>
+        <v>-2.525409304000002</v>
       </c>
       <c r="Q60">
-        <v>-2.327145248000001</v>
+        <v>-2.579409304000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2122890384732732</v>
+        <v>0.216349746728719</v>
       </c>
       <c r="T60">
-        <v>1.99449578076935</v>
+        <v>2.043142019324701</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2280523550646689</v>
+        <v>0.2241870609110304</v>
       </c>
       <c r="W60">
-        <v>0.1133219142765066</v>
+        <v>0.1138893394582608</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8446383520913662</v>
+        <v>0.8303224478186311</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1558981064391486</v>
+        <v>0.1569081064391486</v>
       </c>
       <c r="C61">
-        <v>29.04461040218743</v>
+        <v>25.28861624083859</v>
       </c>
       <c r="D61">
-        <v>154.2306104021874</v>
+        <v>152.8286162408386</v>
       </c>
       <c r="E61">
-        <v>-34.01400000000001</v>
+        <v>-31.66</v>
       </c>
       <c r="F61">
-        <v>138.886</v>
+        <v>141.24</v>
       </c>
       <c r="G61">
         <v>13.7</v>
@@ -6283,37 +6283,37 @@
         <v>16.929</v>
       </c>
       <c r="M61">
-        <v>20.3884648</v>
+        <v>20.734032</v>
       </c>
       <c r="N61">
-        <v>-3.459464800000003</v>
+        <v>-3.805032000000004</v>
       </c>
       <c r="O61">
-        <v>-0.9340554960000008</v>
+        <v>-1.027358640000001</v>
       </c>
       <c r="P61">
-        <v>-2.525409304000002</v>
+        <v>-2.777673360000003</v>
       </c>
       <c r="Q61">
-        <v>-2.579409304000002</v>
+        <v>-2.831673360000003</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.216349746728719</v>
+        <v>0.2206134903969369</v>
       </c>
       <c r="T61">
-        <v>2.043142019324701</v>
+        <v>2.094220569807818</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2241870609110304</v>
+        <v>0.2204506098958466</v>
       </c>
       <c r="W61">
-        <v>0.1138893394582608</v>
+        <v>0.1144378504672897</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8303224478186311</v>
+        <v>0.8164837403549872</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1569081064391486</v>
+        <v>0.1579181064391486</v>
       </c>
       <c r="C62">
-        <v>25.28861624083859</v>
+        <v>21.55788140910093</v>
       </c>
       <c r="D62">
-        <v>152.8286162408386</v>
+        <v>151.4518814091009</v>
       </c>
       <c r="E62">
-        <v>-31.66</v>
+        <v>-29.30600000000001</v>
       </c>
       <c r="F62">
-        <v>141.24</v>
+        <v>143.594</v>
       </c>
       <c r="G62">
         <v>13.7</v>
@@ -6365,37 +6365,37 @@
         <v>16.929</v>
       </c>
       <c r="M62">
-        <v>20.734032</v>
+        <v>21.0795992</v>
       </c>
       <c r="N62">
-        <v>-3.805032000000004</v>
+        <v>-4.150599200000002</v>
       </c>
       <c r="O62">
-        <v>-1.027358640000001</v>
+        <v>-1.120661784000001</v>
       </c>
       <c r="P62">
-        <v>-2.777673360000003</v>
+        <v>-3.029937416000001</v>
       </c>
       <c r="Q62">
-        <v>-2.831673360000003</v>
+        <v>-3.083937416000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2206134903969369</v>
+        <v>0.225095887586602</v>
       </c>
       <c r="T62">
-        <v>2.094220569807818</v>
+        <v>2.147918533136223</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2204506098958466</v>
+        <v>0.2168366654713245</v>
       </c>
       <c r="W62">
-        <v>0.1144378504672897</v>
+        <v>0.1149683775088096</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8164837403549872</v>
+        <v>0.8030987610049055</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1579181064391486</v>
+        <v>0.1952745481348952</v>
       </c>
       <c r="C63">
-        <v>21.55788140910093</v>
+        <v>-18.64673227841688</v>
       </c>
       <c r="D63">
-        <v>151.4518814091009</v>
+        <v>113.6012677215831</v>
       </c>
       <c r="E63">
-        <v>-29.30600000000001</v>
+        <v>-26.952</v>
       </c>
       <c r="F63">
-        <v>143.594</v>
+        <v>145.948</v>
       </c>
       <c r="G63">
         <v>13.7</v>
@@ -6447,45 +6447,45 @@
         <v>16.929</v>
       </c>
       <c r="M63">
-        <v>21.0795992</v>
+        <v>29.3063584</v>
       </c>
       <c r="N63">
-        <v>-4.150599200000002</v>
+        <v>-12.37735840000001</v>
       </c>
       <c r="O63">
-        <v>-1.120661784000001</v>
+        <v>-3.341886768000002</v>
       </c>
       <c r="P63">
-        <v>-3.029937416000001</v>
+        <v>-9.035471632000004</v>
       </c>
       <c r="Q63">
-        <v>-3.083937416000001</v>
+        <v>-9.089471632000004</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.225095887586602</v>
+        <v>0.2373574680382141</v>
       </c>
       <c r="T63">
-        <v>2.147918533136223</v>
+        <v>2.294809107438089</v>
       </c>
       <c r="U63">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.2168366654713245</v>
+        <v>0.155967177416352</v>
       </c>
       <c r="W63">
-        <v>0.1149683775088096</v>
+        <v>0.1694817907747965</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.8030987610049055</v>
+        <v>0.5776562126531557</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1952745481348952</v>
+        <v>0.1968245481348952</v>
       </c>
       <c r="C64">
-        <v>-18.64673227841688</v>
+        <v>-22.16664846318956</v>
       </c>
       <c r="D64">
-        <v>113.6012677215831</v>
+        <v>112.4353515368104</v>
       </c>
       <c r="E64">
-        <v>-26.952</v>
+        <v>-24.59800000000001</v>
       </c>
       <c r="F64">
-        <v>145.948</v>
+        <v>148.302</v>
       </c>
       <c r="G64">
         <v>13.7</v>
@@ -6529,37 +6529,37 @@
         <v>16.929</v>
       </c>
       <c r="M64">
-        <v>29.3063584</v>
+        <v>29.7790416</v>
       </c>
       <c r="N64">
-        <v>-12.37735840000001</v>
+        <v>-12.8500416</v>
       </c>
       <c r="O64">
-        <v>-3.341886768000002</v>
+        <v>-3.469511232</v>
       </c>
       <c r="P64">
-        <v>-9.035471632000004</v>
+        <v>-9.380530368000001</v>
       </c>
       <c r="Q64">
-        <v>-9.089471632000004</v>
+        <v>-9.434530368000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2373574680382141</v>
+        <v>0.2425346969041118</v>
       </c>
       <c r="T64">
-        <v>2.294809107438089</v>
+        <v>2.356830975206685</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.155967177416352</v>
+        <v>0.1534915079335528</v>
       </c>
       <c r="W64">
-        <v>0.1694817907747965</v>
+        <v>0.1699789052069426</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5776562126531557</v>
+        <v>0.568487066420566</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1968245481348952</v>
+        <v>0.1983745481348952</v>
       </c>
       <c r="C65">
-        <v>-22.16664846318956</v>
+        <v>-25.66287563680686</v>
       </c>
       <c r="D65">
-        <v>112.4353515368104</v>
+        <v>111.2931243631931</v>
       </c>
       <c r="E65">
-        <v>-24.59800000000001</v>
+        <v>-22.244</v>
       </c>
       <c r="F65">
-        <v>148.302</v>
+        <v>150.656</v>
       </c>
       <c r="G65">
         <v>13.7</v>
@@ -6611,37 +6611,37 @@
         <v>16.929</v>
       </c>
       <c r="M65">
-        <v>29.7790416</v>
+        <v>30.2517248</v>
       </c>
       <c r="N65">
-        <v>-12.8500416</v>
+        <v>-13.3227248</v>
       </c>
       <c r="O65">
-        <v>-3.469511232</v>
+        <v>-3.597135696000001</v>
       </c>
       <c r="P65">
-        <v>-9.380530368000001</v>
+        <v>-9.725589104000003</v>
       </c>
       <c r="Q65">
-        <v>-9.434530368000001</v>
+        <v>-9.779589104000003</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2425346969041118</v>
+        <v>0.2479995495958927</v>
       </c>
       <c r="T65">
-        <v>2.356830975206685</v>
+        <v>2.42229850229576</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1534915079335528</v>
+        <v>0.1510932031220911</v>
       </c>
       <c r="W65">
-        <v>0.1699789052069426</v>
+        <v>0.1704604848130841</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.568487066420566</v>
+        <v>0.5596044560077447</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1983745481348952</v>
+        <v>0.1999245481348952</v>
       </c>
       <c r="C66">
-        <v>-25.66287563680686</v>
+        <v>-29.1361285063236</v>
       </c>
       <c r="D66">
-        <v>111.2931243631931</v>
+        <v>110.1738714936764</v>
       </c>
       <c r="E66">
-        <v>-22.244</v>
+        <v>-19.88999999999999</v>
       </c>
       <c r="F66">
-        <v>150.656</v>
+        <v>153.01</v>
       </c>
       <c r="G66">
         <v>13.7</v>
@@ -6693,37 +6693,37 @@
         <v>16.929</v>
       </c>
       <c r="M66">
-        <v>30.2517248</v>
+        <v>30.724408</v>
       </c>
       <c r="N66">
-        <v>-13.3227248</v>
+        <v>-13.79540800000001</v>
       </c>
       <c r="O66">
-        <v>-3.597135696000001</v>
+        <v>-3.724760160000002</v>
       </c>
       <c r="P66">
-        <v>-9.725589104000003</v>
+        <v>-10.07064784</v>
       </c>
       <c r="Q66">
-        <v>-9.779589104000003</v>
+        <v>-10.12464784</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2479995495958927</v>
+        <v>0.2537766795843468</v>
       </c>
       <c r="T66">
-        <v>2.42229850229576</v>
+        <v>2.491507030932782</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1510932031220911</v>
+        <v>0.1487686923048281</v>
       </c>
       <c r="W66">
-        <v>0.1704604848130841</v>
+        <v>0.1709272465851905</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5596044560077447</v>
+        <v>0.5509951566845486</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1999245481348952</v>
+        <v>0.2014745481348952</v>
       </c>
       <c r="C67">
-        <v>-29.1361285063236</v>
+        <v>-32.58709331438727</v>
       </c>
       <c r="D67">
-        <v>110.1738714936764</v>
+        <v>109.0769066856127</v>
       </c>
       <c r="E67">
-        <v>-19.88999999999999</v>
+        <v>-17.536</v>
       </c>
       <c r="F67">
-        <v>153.01</v>
+        <v>155.364</v>
       </c>
       <c r="G67">
         <v>13.7</v>
@@ -6775,37 +6775,37 @@
         <v>16.929</v>
       </c>
       <c r="M67">
-        <v>30.724408</v>
+        <v>31.1970912</v>
       </c>
       <c r="N67">
-        <v>-13.79540800000001</v>
+        <v>-14.2680912</v>
       </c>
       <c r="O67">
-        <v>-3.724760160000002</v>
+        <v>-3.852384624000001</v>
       </c>
       <c r="P67">
-        <v>-10.07064784</v>
+        <v>-10.415706576</v>
       </c>
       <c r="Q67">
-        <v>-10.12464784</v>
+        <v>-10.469706576</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2537766795843468</v>
+        <v>0.2598936407485923</v>
       </c>
       <c r="T67">
-        <v>2.491507030932782</v>
+        <v>2.564786649489629</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1487686923048281</v>
+        <v>0.1465146212093004</v>
       </c>
       <c r="W67">
-        <v>0.1709272465851905</v>
+        <v>0.1713798640611725</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5509951566845486</v>
+        <v>0.5426467452196311</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2014745481348952</v>
+        <v>0.2030245481348952</v>
       </c>
       <c r="C68">
-        <v>-32.58709331438727</v>
+        <v>-36.01642924232168</v>
       </c>
       <c r="D68">
-        <v>109.0769066856127</v>
+        <v>108.0015707576783</v>
       </c>
       <c r="E68">
-        <v>-17.536</v>
+        <v>-15.18199999999999</v>
       </c>
       <c r="F68">
-        <v>155.364</v>
+        <v>157.718</v>
       </c>
       <c r="G68">
         <v>13.7</v>
@@ -6857,37 +6857,37 @@
         <v>16.929</v>
       </c>
       <c r="M68">
-        <v>31.1970912</v>
+        <v>31.6697744</v>
       </c>
       <c r="N68">
-        <v>-14.2680912</v>
+        <v>-14.74077440000001</v>
       </c>
       <c r="O68">
-        <v>-3.852384624000001</v>
+        <v>-3.980009088000002</v>
       </c>
       <c r="P68">
-        <v>-10.415706576</v>
+        <v>-10.760765312</v>
       </c>
       <c r="Q68">
-        <v>-10.469706576</v>
+        <v>-10.814765312</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2598936407485923</v>
+        <v>0.2663813268318829</v>
       </c>
       <c r="T68">
-        <v>2.564786649489629</v>
+        <v>2.64250745704992</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1465146212093004</v>
+        <v>0.1443278358181168</v>
       </c>
       <c r="W68">
-        <v>0.1713798640611725</v>
+        <v>0.1718189705677222</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5426467452196311</v>
+        <v>0.5345475400670994</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2030245481348952</v>
+        <v>0.2045745481348952</v>
       </c>
       <c r="C69">
-        <v>-36.01642924232168</v>
+        <v>-39.42476973102629</v>
       </c>
       <c r="D69">
-        <v>108.0015707576783</v>
+        <v>106.9472302689737</v>
       </c>
       <c r="E69">
-        <v>-15.18199999999999</v>
+        <v>-12.828</v>
       </c>
       <c r="F69">
-        <v>157.718</v>
+        <v>160.072</v>
       </c>
       <c r="G69">
         <v>13.7</v>
@@ -6939,37 +6939,37 @@
         <v>16.929</v>
       </c>
       <c r="M69">
-        <v>31.6697744</v>
+        <v>32.1424576</v>
       </c>
       <c r="N69">
-        <v>-14.74077440000001</v>
+        <v>-15.2134576</v>
       </c>
       <c r="O69">
-        <v>-3.980009088000002</v>
+        <v>-4.107633552000001</v>
       </c>
       <c r="P69">
-        <v>-10.760765312</v>
+        <v>-11.105824048</v>
       </c>
       <c r="Q69">
-        <v>-10.814765312</v>
+        <v>-11.159824048</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2663813268318829</v>
+        <v>0.2732744932953793</v>
       </c>
       <c r="T69">
-        <v>2.64250745704992</v>
+        <v>2.725085815082731</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1443278358181168</v>
+        <v>0.142205367644321</v>
       </c>
       <c r="W69">
-        <v>0.1718189705677222</v>
+        <v>0.1722451621770204</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5345475400670994</v>
+        <v>0.5266865468308185</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2045745481348952</v>
+        <v>0.2061245481348952</v>
       </c>
       <c r="C70">
-        <v>-39.42476973102629</v>
+        <v>-42.81272372525451</v>
       </c>
       <c r="D70">
-        <v>106.9472302689737</v>
+        <v>105.9132762747455</v>
       </c>
       <c r="E70">
-        <v>-12.828</v>
+        <v>-10.47399999999999</v>
       </c>
       <c r="F70">
-        <v>160.072</v>
+        <v>162.426</v>
       </c>
       <c r="G70">
         <v>13.7</v>
@@ -7021,37 +7021,37 @@
         <v>16.929</v>
       </c>
       <c r="M70">
-        <v>32.1424576</v>
+        <v>32.61514080000001</v>
       </c>
       <c r="N70">
-        <v>-15.2134576</v>
+        <v>-15.68614080000001</v>
       </c>
       <c r="O70">
-        <v>-4.107633552000001</v>
+        <v>-4.235258016000002</v>
       </c>
       <c r="P70">
-        <v>-11.105824048</v>
+        <v>-11.450882784</v>
       </c>
       <c r="Q70">
-        <v>-11.159824048</v>
+        <v>-11.504882784</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2732744932953793</v>
+        <v>0.2806123801758754</v>
       </c>
       <c r="T70">
-        <v>2.725085815082731</v>
+        <v>2.812991809117657</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.142205367644321</v>
+        <v>0.1401444202871569</v>
       </c>
       <c r="W70">
-        <v>0.1722451621770204</v>
+        <v>0.1726590004063389</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5266865468308185</v>
+        <v>0.5190534084709515</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2061245481348952</v>
+        <v>0.2076745481348952</v>
       </c>
       <c r="C71">
-        <v>-42.81272372525451</v>
+        <v>-46.18087684640517</v>
       </c>
       <c r="D71">
-        <v>105.9132762747455</v>
+        <v>104.8991231535949</v>
       </c>
       <c r="E71">
-        <v>-10.47399999999999</v>
+        <v>-8.119999999999976</v>
       </c>
       <c r="F71">
-        <v>162.426</v>
+        <v>164.78</v>
       </c>
       <c r="G71">
         <v>13.7</v>
@@ -7103,37 +7103,37 @@
         <v>16.929</v>
       </c>
       <c r="M71">
-        <v>32.61514080000001</v>
+        <v>33.087824</v>
       </c>
       <c r="N71">
-        <v>-15.68614080000001</v>
+        <v>-16.15882400000001</v>
       </c>
       <c r="O71">
-        <v>-4.235258016000002</v>
+        <v>-4.362882480000002</v>
       </c>
       <c r="P71">
-        <v>-11.450882784</v>
+        <v>-11.79594152</v>
       </c>
       <c r="Q71">
-        <v>-11.504882784</v>
+        <v>-11.84994152</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2806123801758754</v>
+        <v>0.2884394595150713</v>
       </c>
       <c r="T71">
-        <v>2.812991809117657</v>
+        <v>2.906758202754913</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1401444202871569</v>
+        <v>0.1381423571401975</v>
       </c>
       <c r="W71">
-        <v>0.1726590004063389</v>
+        <v>0.1730610146862483</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5190534084709515</v>
+        <v>0.5116383597785094</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2076745481348952</v>
+        <v>0.2092245481348952</v>
       </c>
       <c r="C72">
-        <v>-46.18087684640517</v>
+        <v>-49.52979249857428</v>
       </c>
       <c r="D72">
-        <v>104.8991231535949</v>
+        <v>103.9042075014257</v>
       </c>
       <c r="E72">
-        <v>-8.119999999999976</v>
+        <v>-5.765999999999991</v>
       </c>
       <c r="F72">
-        <v>164.78</v>
+        <v>167.134</v>
       </c>
       <c r="G72">
         <v>13.7</v>
@@ -7185,37 +7185,37 @@
         <v>16.929</v>
       </c>
       <c r="M72">
-        <v>33.087824</v>
+        <v>33.5605072</v>
       </c>
       <c r="N72">
-        <v>-16.15882400000001</v>
+        <v>-16.63150720000001</v>
       </c>
       <c r="O72">
-        <v>-4.362882480000002</v>
+        <v>-4.490506944000002</v>
       </c>
       <c r="P72">
-        <v>-11.79594152</v>
+        <v>-12.141000256</v>
       </c>
       <c r="Q72">
-        <v>-11.84994152</v>
+        <v>-12.195000256</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2884394595150713</v>
+        <v>0.2968063374293841</v>
       </c>
       <c r="T72">
-        <v>2.906758202754913</v>
+        <v>3.006991244229221</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1381423571401975</v>
+        <v>0.1361966901382229</v>
       </c>
       <c r="W72">
-        <v>0.1730610146862483</v>
+        <v>0.1734517046202448</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5116383597785094</v>
+        <v>0.5044321856971219</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2092245481348952</v>
+        <v>0.2371311919819051</v>
       </c>
       <c r="C73">
-        <v>-49.52979249857425</v>
+        <v>-67.03875851803191</v>
       </c>
       <c r="D73">
-        <v>103.9042075014257</v>
+        <v>88.74924148196808</v>
       </c>
       <c r="E73">
-        <v>-5.76600000000002</v>
+        <v>-3.412000000000006</v>
       </c>
       <c r="F73">
-        <v>167.134</v>
+        <v>169.488</v>
       </c>
       <c r="G73">
         <v>13.7</v>
@@ -7267,45 +7267,45 @@
         <v>16.929</v>
       </c>
       <c r="M73">
-        <v>33.5605072</v>
+        <v>39.9652704</v>
       </c>
       <c r="N73">
-        <v>-16.6315072</v>
+        <v>-23.0362704</v>
       </c>
       <c r="O73">
-        <v>-4.490506944</v>
+        <v>-6.219793008000001</v>
       </c>
       <c r="P73">
-        <v>-12.141000256</v>
+        <v>-16.816477392</v>
       </c>
       <c r="Q73">
-        <v>-12.195000256</v>
+        <v>-16.870477392</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.296806337429384</v>
+        <v>0.3099017203626115</v>
       </c>
       <c r="T73">
-        <v>3.006991244229219</v>
+        <v>3.163870557410394</v>
       </c>
       <c r="U73">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1361966901382229</v>
+        <v>0.1143700506527788</v>
       </c>
       <c r="W73">
-        <v>0.1734517046202448</v>
+        <v>0.2088315420560748</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.504432185697122</v>
+        <v>0.4235927801954769</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2371311919819051</v>
+        <v>0.2390311919819051</v>
       </c>
       <c r="C74">
-        <v>-67.03875851803191</v>
+        <v>-70.26541037659692</v>
       </c>
       <c r="D74">
-        <v>88.74924148196808</v>
+        <v>87.87658962340309</v>
       </c>
       <c r="E74">
-        <v>-3.412000000000006</v>
+        <v>-1.057999999999993</v>
       </c>
       <c r="F74">
-        <v>169.488</v>
+        <v>171.842</v>
       </c>
       <c r="G74">
         <v>13.7</v>
@@ -7349,37 +7349,37 @@
         <v>16.929</v>
       </c>
       <c r="M74">
-        <v>39.9652704</v>
+        <v>40.5203436</v>
       </c>
       <c r="N74">
-        <v>-23.0362704</v>
+        <v>-23.59134360000001</v>
       </c>
       <c r="O74">
-        <v>-6.219793008000001</v>
+        <v>-6.369662772000002</v>
       </c>
       <c r="P74">
-        <v>-16.816477392</v>
+        <v>-17.221680828</v>
       </c>
       <c r="Q74">
-        <v>-16.870477392</v>
+        <v>-17.275680828</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3099017203626115</v>
+        <v>0.3196832655612268</v>
       </c>
       <c r="T74">
-        <v>3.163870557410394</v>
+        <v>3.281050948425594</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1143700506527788</v>
+        <v>0.1128033376301379</v>
       </c>
       <c r="W74">
-        <v>0.2088315420560748</v>
+        <v>0.2092009729868135</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4235927801954769</v>
+        <v>0.4177901393708813</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2390311919819051</v>
+        <v>0.2409311919819051</v>
       </c>
       <c r="C75">
-        <v>-70.26541037659692</v>
+        <v>-73.47506814503787</v>
       </c>
       <c r="D75">
-        <v>87.87658962340309</v>
+        <v>87.02093185496213</v>
       </c>
       <c r="E75">
-        <v>-1.057999999999993</v>
+        <v>1.295999999999992</v>
       </c>
       <c r="F75">
-        <v>171.842</v>
+        <v>174.196</v>
       </c>
       <c r="G75">
         <v>13.7</v>
@@ -7431,37 +7431,37 @@
         <v>16.929</v>
       </c>
       <c r="M75">
-        <v>40.5203436</v>
+        <v>41.0754168</v>
       </c>
       <c r="N75">
-        <v>-23.59134360000001</v>
+        <v>-24.1464168</v>
       </c>
       <c r="O75">
-        <v>-6.369662772000002</v>
+        <v>-6.519532536000001</v>
       </c>
       <c r="P75">
-        <v>-17.221680828</v>
+        <v>-17.626884264</v>
       </c>
       <c r="Q75">
-        <v>-17.275680828</v>
+        <v>-17.680884264</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3196832655612268</v>
+        <v>0.3302172373135817</v>
       </c>
       <c r="T75">
-        <v>3.281050948425594</v>
+        <v>3.407245215672732</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1128033376301379</v>
+        <v>0.1112789682027037</v>
       </c>
       <c r="W75">
-        <v>0.2092009729868135</v>
+        <v>0.2095604192978025</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4177901393708813</v>
+        <v>0.4121443266766802</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2409311919819051</v>
+        <v>0.2428311919819051</v>
       </c>
       <c r="C76">
-        <v>-73.47506814503787</v>
+        <v>-76.66822345268895</v>
       </c>
       <c r="D76">
-        <v>87.02093185496213</v>
+        <v>86.18177654731106</v>
       </c>
       <c r="E76">
-        <v>1.295999999999992</v>
+        <v>3.650000000000006</v>
       </c>
       <c r="F76">
-        <v>174.196</v>
+        <v>176.55</v>
       </c>
       <c r="G76">
         <v>13.7</v>
@@ -7513,37 +7513,37 @@
         <v>16.929</v>
       </c>
       <c r="M76">
-        <v>41.0754168</v>
+        <v>41.63049</v>
       </c>
       <c r="N76">
-        <v>-24.1464168</v>
+        <v>-24.70149</v>
       </c>
       <c r="O76">
-        <v>-6.519532536000001</v>
+        <v>-6.669402300000002</v>
       </c>
       <c r="P76">
-        <v>-17.626884264</v>
+        <v>-18.0320877</v>
       </c>
       <c r="Q76">
-        <v>-17.680884264</v>
+        <v>-18.0860877</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3302172373135817</v>
+        <v>0.341593926806125</v>
       </c>
       <c r="T76">
-        <v>3.407245215672732</v>
+        <v>3.543535024299642</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1112789682027037</v>
+        <v>0.1097952486266676</v>
       </c>
       <c r="W76">
-        <v>0.2095604192978025</v>
+        <v>0.2099102803738318</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4121443266766802</v>
+        <v>0.4066490689876577</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2428311919819051</v>
+        <v>0.2447311919819051</v>
       </c>
       <c r="C77">
-        <v>-76.66822345268895</v>
+        <v>-79.84534914659613</v>
       </c>
       <c r="D77">
-        <v>86.18177654731106</v>
+        <v>85.35865085340386</v>
       </c>
       <c r="E77">
-        <v>3.650000000000006</v>
+        <v>6.003999999999991</v>
       </c>
       <c r="F77">
-        <v>176.55</v>
+        <v>178.904</v>
       </c>
       <c r="G77">
         <v>13.7</v>
@@ -7595,37 +7595,37 @@
         <v>16.929</v>
       </c>
       <c r="M77">
-        <v>41.63049</v>
+        <v>42.1855632</v>
       </c>
       <c r="N77">
-        <v>-24.70149</v>
+        <v>-25.25656320000001</v>
       </c>
       <c r="O77">
-        <v>-6.669402300000002</v>
+        <v>-6.819272064000002</v>
       </c>
       <c r="P77">
-        <v>-18.0320877</v>
+        <v>-18.437291136</v>
       </c>
       <c r="Q77">
-        <v>-18.0860877</v>
+        <v>-18.491291136</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.341593926806125</v>
+        <v>0.3539186737563802</v>
       </c>
       <c r="T77">
-        <v>3.543535024299642</v>
+        <v>3.691182316978793</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1097952486266676</v>
+        <v>0.1083505743026325</v>
       </c>
       <c r="W77">
-        <v>0.2099102803738318</v>
+        <v>0.2102509345794393</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4066490689876577</v>
+        <v>0.4012984233430833</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2447311919819051</v>
+        <v>0.2466311919819051</v>
       </c>
       <c r="C78">
-        <v>-79.84534914659613</v>
+        <v>-83.00690017998383</v>
       </c>
       <c r="D78">
-        <v>85.35865085340386</v>
+        <v>84.55109982001618</v>
       </c>
       <c r="E78">
-        <v>6.003999999999991</v>
+        <v>8.358000000000004</v>
       </c>
       <c r="F78">
-        <v>178.904</v>
+        <v>181.258</v>
       </c>
       <c r="G78">
         <v>13.7</v>
@@ -7677,37 +7677,37 @@
         <v>16.929</v>
       </c>
       <c r="M78">
-        <v>42.1855632</v>
+        <v>42.74063640000001</v>
       </c>
       <c r="N78">
-        <v>-25.25656320000001</v>
+        <v>-25.81163640000001</v>
       </c>
       <c r="O78">
-        <v>-6.819272064000002</v>
+        <v>-6.969141828000002</v>
       </c>
       <c r="P78">
-        <v>-18.437291136</v>
+        <v>-18.84249457200001</v>
       </c>
       <c r="Q78">
-        <v>-18.491291136</v>
+        <v>-18.89649457200001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3539186737563802</v>
+        <v>0.3673151378327446</v>
       </c>
       <c r="T78">
-        <v>3.691182316978793</v>
+        <v>3.851668504673524</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1083505743026325</v>
+        <v>0.1069434239870139</v>
       </c>
       <c r="W78">
-        <v>0.2102509345794393</v>
+        <v>0.2105827406238621</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4012984233430833</v>
+        <v>0.3960867555074589</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2466311919819051</v>
+        <v>0.2485311919819051</v>
       </c>
       <c r="C79">
-        <v>-83.00690017998383</v>
+        <v>-86.15331445076053</v>
       </c>
       <c r="D79">
-        <v>84.55109982001618</v>
+        <v>83.75868554923949</v>
       </c>
       <c r="E79">
-        <v>8.358000000000004</v>
+        <v>10.71200000000002</v>
       </c>
       <c r="F79">
-        <v>181.258</v>
+        <v>183.612</v>
       </c>
       <c r="G79">
         <v>13.7</v>
@@ -7759,37 +7759,37 @@
         <v>16.929</v>
       </c>
       <c r="M79">
-        <v>42.74063640000001</v>
+        <v>43.29570960000001</v>
       </c>
       <c r="N79">
-        <v>-25.81163640000001</v>
+        <v>-26.36670960000001</v>
       </c>
       <c r="O79">
-        <v>-6.969141828000002</v>
+        <v>-7.119011592000003</v>
       </c>
       <c r="P79">
-        <v>-18.84249457200001</v>
+        <v>-19.24769800800001</v>
       </c>
       <c r="Q79">
-        <v>-18.89649457200001</v>
+        <v>-19.30169800800001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3673151378327446</v>
+        <v>0.3819294622796875</v>
       </c>
       <c r="T79">
-        <v>3.851668504673524</v>
+        <v>4.026744345795048</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1069434239870139</v>
+        <v>0.1055723544487188</v>
       </c>
       <c r="W79">
-        <v>0.2105827406238621</v>
+        <v>0.2109060388209921</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3960867555074589</v>
+        <v>0.3910087201804401</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2485311919819051</v>
+        <v>0.2504311919819051</v>
       </c>
       <c r="C80">
-        <v>-86.15331445076053</v>
+        <v>-89.28501359331169</v>
       </c>
       <c r="D80">
-        <v>83.75868554923949</v>
+        <v>82.98098640668832</v>
       </c>
       <c r="E80">
-        <v>10.71200000000002</v>
+        <v>13.066</v>
       </c>
       <c r="F80">
-        <v>183.612</v>
+        <v>185.966</v>
       </c>
       <c r="G80">
         <v>13.7</v>
@@ -7841,37 +7841,37 @@
         <v>16.929</v>
       </c>
       <c r="M80">
-        <v>43.29570960000001</v>
+        <v>43.8507828</v>
       </c>
       <c r="N80">
-        <v>-26.36670960000001</v>
+        <v>-26.92178280000001</v>
       </c>
       <c r="O80">
-        <v>-7.119011592000003</v>
+        <v>-7.268881356000002</v>
       </c>
       <c r="P80">
-        <v>-19.24769800800001</v>
+        <v>-19.652901444</v>
       </c>
       <c r="Q80">
-        <v>-19.30169800800001</v>
+        <v>-19.706901444</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3819294622796875</v>
+        <v>0.3979356271501489</v>
       </c>
       <c r="T80">
-        <v>4.026744345795048</v>
+        <v>4.218494076547193</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1055723544487188</v>
+        <v>0.1042359955316465</v>
       </c>
       <c r="W80">
-        <v>0.2109060388209921</v>
+        <v>0.2112211522536378</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3910087201804401</v>
+        <v>0.3860592427098016</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2504311919819051</v>
+        <v>0.2523311919819051</v>
       </c>
       <c r="C81">
-        <v>-89.28501359331169</v>
+        <v>-92.40240372658766</v>
       </c>
       <c r="D81">
-        <v>82.98098640668832</v>
+        <v>82.21759627341235</v>
       </c>
       <c r="E81">
-        <v>13.066</v>
+        <v>15.42000000000002</v>
       </c>
       <c r="F81">
-        <v>185.966</v>
+        <v>188.32</v>
       </c>
       <c r="G81">
         <v>13.7</v>
@@ -7923,37 +7923,37 @@
         <v>16.929</v>
       </c>
       <c r="M81">
-        <v>43.8507828</v>
+        <v>44.40585600000001</v>
       </c>
       <c r="N81">
-        <v>-26.92178280000001</v>
+        <v>-27.47685600000001</v>
       </c>
       <c r="O81">
-        <v>-7.268881356000002</v>
+        <v>-7.418751120000003</v>
       </c>
       <c r="P81">
-        <v>-19.652901444</v>
+        <v>-20.05810488000001</v>
       </c>
       <c r="Q81">
-        <v>-19.706901444</v>
+        <v>-20.11210488</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3979356271501489</v>
+        <v>0.4155424085076563</v>
       </c>
       <c r="T81">
-        <v>4.218494076547193</v>
+        <v>4.429418780374553</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1042359955316465</v>
+        <v>0.1029330455875009</v>
       </c>
       <c r="W81">
-        <v>0.2112211522536378</v>
+        <v>0.2115283878504673</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3860592427098016</v>
+        <v>0.3812335021759291</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2523311919819051</v>
+        <v>0.2542311919819051</v>
       </c>
       <c r="C82">
-        <v>-92.40240372658766</v>
+        <v>-95.50587616127507</v>
       </c>
       <c r="D82">
-        <v>82.21759627341235</v>
+        <v>81.46812383872494</v>
       </c>
       <c r="E82">
-        <v>15.42000000000002</v>
+        <v>17.774</v>
       </c>
       <c r="F82">
-        <v>188.32</v>
+        <v>190.674</v>
       </c>
       <c r="G82">
         <v>13.7</v>
@@ -8005,37 +8005,37 @@
         <v>16.929</v>
       </c>
       <c r="M82">
-        <v>44.40585600000001</v>
+        <v>44.9609292</v>
       </c>
       <c r="N82">
-        <v>-27.47685600000001</v>
+        <v>-28.0319292</v>
       </c>
       <c r="O82">
-        <v>-7.418751120000003</v>
+        <v>-7.568620884000001</v>
       </c>
       <c r="P82">
-        <v>-20.05810488000001</v>
+        <v>-20.463308316</v>
       </c>
       <c r="Q82">
-        <v>-20.11210488</v>
+        <v>-20.517308316</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4155424085076563</v>
+        <v>0.4350025352712171</v>
       </c>
       <c r="T82">
-        <v>4.429418780374553</v>
+        <v>4.662546084604792</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1029330455875009</v>
+        <v>0.1016622672469144</v>
       </c>
       <c r="W82">
-        <v>0.2115283878504673</v>
+        <v>0.2118280373831776</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3812335021759291</v>
+        <v>0.3765269157293127</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2542311919819051</v>
+        <v>0.2561311919819051</v>
       </c>
       <c r="C83">
-        <v>-95.50587616127507</v>
+        <v>-98.59580806863998</v>
       </c>
       <c r="D83">
-        <v>81.46812383872494</v>
+        <v>80.73219193136003</v>
       </c>
       <c r="E83">
-        <v>17.774</v>
+        <v>20.12800000000001</v>
       </c>
       <c r="F83">
-        <v>190.674</v>
+        <v>193.028</v>
       </c>
       <c r="G83">
         <v>13.7</v>
@@ -8087,37 +8087,37 @@
         <v>16.929</v>
       </c>
       <c r="M83">
-        <v>44.9609292</v>
+        <v>45.5160024</v>
       </c>
       <c r="N83">
-        <v>-28.0319292</v>
+        <v>-28.58700240000001</v>
       </c>
       <c r="O83">
-        <v>-7.568620884000001</v>
+        <v>-7.718490648000002</v>
       </c>
       <c r="P83">
-        <v>-20.463308316</v>
+        <v>-20.868511752</v>
       </c>
       <c r="Q83">
-        <v>-20.517308316</v>
+        <v>-20.922511752</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4350025352712171</v>
+        <v>0.4566248983418404</v>
       </c>
       <c r="T83">
-        <v>4.662546084604792</v>
+        <v>4.921576422638393</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1016622672469144</v>
+        <v>0.1004224835000009</v>
       </c>
       <c r="W83">
-        <v>0.2118280373831776</v>
+        <v>0.2121203783906998</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3765269157293127</v>
+        <v>0.3719351240740773</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2561311919819051</v>
+        <v>0.2580311919819051</v>
       </c>
       <c r="C84">
-        <v>-98.59580806863998</v>
+        <v>-101.6725631134435</v>
       </c>
       <c r="D84">
-        <v>80.73219193136003</v>
+        <v>80.00943688655654</v>
       </c>
       <c r="E84">
-        <v>20.12800000000001</v>
+        <v>22.48200000000003</v>
       </c>
       <c r="F84">
-        <v>193.028</v>
+        <v>195.382</v>
       </c>
       <c r="G84">
         <v>13.7</v>
@@ -8169,37 +8169,37 @@
         <v>16.929</v>
       </c>
       <c r="M84">
-        <v>45.5160024</v>
+        <v>46.07107560000001</v>
       </c>
       <c r="N84">
-        <v>-28.58700240000001</v>
+        <v>-29.14207560000001</v>
       </c>
       <c r="O84">
-        <v>-7.718490648000002</v>
+        <v>-7.868360412000003</v>
       </c>
       <c r="P84">
-        <v>-20.868511752</v>
+        <v>-21.273715188</v>
       </c>
       <c r="Q84">
-        <v>-20.922511752</v>
+        <v>-21.327715188</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4566248983418404</v>
+        <v>0.4807910688325369</v>
       </c>
       <c r="T84">
-        <v>4.921576422638393</v>
+        <v>5.21108091808771</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1004224835000009</v>
+        <v>0.09921257406024181</v>
       </c>
       <c r="W84">
-        <v>0.2121203783906998</v>
+        <v>0.212405675036595</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3719351240740773</v>
+        <v>0.3674539780008955</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2580311919819051</v>
+        <v>0.2599311919819051</v>
       </c>
       <c r="C85">
-        <v>-101.6725631134435</v>
+        <v>-104.7364920531624</v>
       </c>
       <c r="D85">
-        <v>80.00943688655654</v>
+        <v>79.29950794683764</v>
       </c>
       <c r="E85">
-        <v>22.48200000000003</v>
+        <v>24.83600000000001</v>
       </c>
       <c r="F85">
-        <v>195.382</v>
+        <v>197.736</v>
       </c>
       <c r="G85">
         <v>13.7</v>
@@ -8251,37 +8251,37 @@
         <v>16.929</v>
       </c>
       <c r="M85">
-        <v>46.07107560000001</v>
+        <v>46.6261488</v>
       </c>
       <c r="N85">
-        <v>-29.14207560000001</v>
+        <v>-29.6971488</v>
       </c>
       <c r="O85">
-        <v>-7.868360412000003</v>
+        <v>-8.018230176000001</v>
       </c>
       <c r="P85">
-        <v>-21.273715188</v>
+        <v>-21.678918624</v>
       </c>
       <c r="Q85">
-        <v>-21.327715188</v>
+        <v>-21.732918624</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4807910688325369</v>
+        <v>0.5079780106345705</v>
       </c>
       <c r="T85">
-        <v>5.21108091808771</v>
+        <v>5.536773475468193</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09921257406024181</v>
+        <v>0.09803147198809607</v>
       </c>
       <c r="W85">
-        <v>0.212405675036595</v>
+        <v>0.212684178905207</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3674539780008955</v>
+        <v>0.3630795258818373</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2599311919819051</v>
+        <v>0.2618311919819051</v>
       </c>
       <c r="C86">
-        <v>-104.7364920531624</v>
+        <v>-107.7879333055886</v>
       </c>
       <c r="D86">
-        <v>79.29950794683764</v>
+        <v>78.60206669441139</v>
       </c>
       <c r="E86">
-        <v>24.83599999999998</v>
+        <v>27.19</v>
       </c>
       <c r="F86">
-        <v>197.736</v>
+        <v>200.09</v>
       </c>
       <c r="G86">
         <v>13.7</v>
@@ -8333,37 +8333,37 @@
         <v>16.929</v>
       </c>
       <c r="M86">
-        <v>46.6261488</v>
+        <v>47.18122200000001</v>
       </c>
       <c r="N86">
-        <v>-29.6971488</v>
+        <v>-30.25222200000001</v>
       </c>
       <c r="O86">
-        <v>-8.018230176000001</v>
+        <v>-8.168099940000003</v>
       </c>
       <c r="P86">
-        <v>-21.678918624</v>
+        <v>-22.08412206000001</v>
       </c>
       <c r="Q86">
-        <v>-21.732918624</v>
+        <v>-22.13812206</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5079780106345702</v>
+        <v>0.5387898780102082</v>
       </c>
       <c r="T86">
-        <v>5.536773475468189</v>
+        <v>5.905891707166068</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09803147198809607</v>
+        <v>0.096878160552942</v>
       </c>
       <c r="W86">
-        <v>0.212684178905207</v>
+        <v>0.2129561297416163</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3630795258818373</v>
+        <v>0.3588080020479333</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2618311919819051</v>
+        <v>0.2637311919819051</v>
       </c>
       <c r="C87">
-        <v>-107.7879333055886</v>
+        <v>-110.8272134867376</v>
       </c>
       <c r="D87">
-        <v>78.60206669441139</v>
+        <v>77.91678651326237</v>
       </c>
       <c r="E87">
-        <v>27.19</v>
+        <v>29.54399999999998</v>
       </c>
       <c r="F87">
-        <v>200.09</v>
+        <v>202.444</v>
       </c>
       <c r="G87">
         <v>13.7</v>
@@ -8415,37 +8415,37 @@
         <v>16.929</v>
       </c>
       <c r="M87">
-        <v>47.18122200000001</v>
+        <v>47.7362952</v>
       </c>
       <c r="N87">
-        <v>-30.25222200000001</v>
+        <v>-30.8072952</v>
       </c>
       <c r="O87">
-        <v>-8.168099940000003</v>
+        <v>-8.317969704000001</v>
       </c>
       <c r="P87">
-        <v>-22.08412206000001</v>
+        <v>-22.489325496</v>
       </c>
       <c r="Q87">
-        <v>-22.13812206</v>
+        <v>-22.543325496</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5387898780102082</v>
+        <v>0.574003440725223</v>
       </c>
       <c r="T87">
-        <v>5.905891707166068</v>
+        <v>6.327741114820787</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.096878160552942</v>
+        <v>0.09575167031395432</v>
       </c>
       <c r="W87">
-        <v>0.2129561297416163</v>
+        <v>0.2132217561399696</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3588080020479333</v>
+        <v>0.3546358159776085</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2637311919819051</v>
+        <v>0.2656311919819051</v>
       </c>
       <c r="C88">
-        <v>-110.8272134867376</v>
+        <v>-113.8546479208619</v>
       </c>
       <c r="D88">
-        <v>77.91678651326237</v>
+        <v>77.24335207913809</v>
       </c>
       <c r="E88">
-        <v>29.54399999999998</v>
+        <v>31.898</v>
       </c>
       <c r="F88">
-        <v>202.444</v>
+        <v>204.798</v>
       </c>
       <c r="G88">
         <v>13.7</v>
@@ -8497,37 +8497,37 @@
         <v>16.929</v>
       </c>
       <c r="M88">
-        <v>47.7362952</v>
+        <v>48.2913684</v>
       </c>
       <c r="N88">
-        <v>-30.8072952</v>
+        <v>-31.3623684</v>
       </c>
       <c r="O88">
-        <v>-8.317969704000001</v>
+        <v>-8.467839468000001</v>
       </c>
       <c r="P88">
-        <v>-22.489325496</v>
+        <v>-22.894528932</v>
       </c>
       <c r="Q88">
-        <v>-22.543325496</v>
+        <v>-22.948528932</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.574003440725223</v>
+        <v>0.6146344746271633</v>
       </c>
       <c r="T88">
-        <v>6.327741114820787</v>
+        <v>6.814490431345464</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09575167031395432</v>
+        <v>0.09465107640229967</v>
       </c>
       <c r="W88">
-        <v>0.2132217561399696</v>
+        <v>0.2134812761843378</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3546358159776085</v>
+        <v>0.3505595422307395</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2656311919819051</v>
+        <v>0.2675311919819051</v>
       </c>
       <c r="C89">
-        <v>-113.8546479208619</v>
+        <v>-116.8705411242428</v>
       </c>
       <c r="D89">
-        <v>77.24335207913809</v>
+        <v>76.58145887575721</v>
       </c>
       <c r="E89">
-        <v>31.898</v>
+        <v>34.25200000000001</v>
       </c>
       <c r="F89">
-        <v>204.798</v>
+        <v>207.152</v>
       </c>
       <c r="G89">
         <v>13.7</v>
@@ -8579,37 +8579,37 @@
         <v>16.929</v>
       </c>
       <c r="M89">
-        <v>48.2913684</v>
+        <v>48.84644160000001</v>
       </c>
       <c r="N89">
-        <v>-31.3623684</v>
+        <v>-31.91744160000001</v>
       </c>
       <c r="O89">
-        <v>-8.467839468000001</v>
+        <v>-8.617709232000003</v>
       </c>
       <c r="P89">
-        <v>-22.894528932</v>
+        <v>-23.299732368</v>
       </c>
       <c r="Q89">
-        <v>-22.948528932</v>
+        <v>-23.353732368</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6146344746271633</v>
+        <v>0.6620373475127604</v>
       </c>
       <c r="T89">
-        <v>6.814490431345464</v>
+        <v>7.382364633957588</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09465107640229967</v>
+        <v>0.09357549598863717</v>
       </c>
       <c r="W89">
-        <v>0.2134812761843378</v>
+        <v>0.2137348980458794</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3505595422307395</v>
+        <v>0.3465759110690265</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2675311919819051</v>
+        <v>0.2694311919819051</v>
       </c>
       <c r="C90">
-        <v>-116.8705411242428</v>
+        <v>-119.8751872643202</v>
       </c>
       <c r="D90">
-        <v>76.58145887575721</v>
+        <v>75.93081273567981</v>
       </c>
       <c r="E90">
-        <v>34.25200000000001</v>
+        <v>36.60599999999999</v>
       </c>
       <c r="F90">
-        <v>207.152</v>
+        <v>209.506</v>
       </c>
       <c r="G90">
         <v>13.7</v>
@@ -8661,37 +8661,37 @@
         <v>16.929</v>
       </c>
       <c r="M90">
-        <v>48.84644160000001</v>
+        <v>49.4015148</v>
       </c>
       <c r="N90">
-        <v>-31.91744160000001</v>
+        <v>-32.4725148</v>
       </c>
       <c r="O90">
-        <v>-8.617709232000003</v>
+        <v>-8.767578996000001</v>
       </c>
       <c r="P90">
-        <v>-23.299732368</v>
+        <v>-23.704935804</v>
       </c>
       <c r="Q90">
-        <v>-23.353732368</v>
+        <v>-23.758935804</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6620373475127604</v>
+        <v>0.7180589245593749</v>
       </c>
       <c r="T90">
-        <v>7.382364633957588</v>
+        <v>8.053488691590095</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09357549598863717</v>
+        <v>0.09252408592134911</v>
       </c>
       <c r="W90">
-        <v>0.2137348980458794</v>
+        <v>0.2139828205397459</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3465759110690265</v>
+        <v>0.3426817997087005</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2694311919819051</v>
+        <v>0.271331191981905</v>
       </c>
       <c r="C91">
-        <v>-119.8751872643202</v>
+        <v>-122.8688705956146</v>
       </c>
       <c r="D91">
-        <v>75.93081273567981</v>
+        <v>75.29112940438537</v>
       </c>
       <c r="E91">
-        <v>36.60599999999999</v>
+        <v>38.96000000000001</v>
       </c>
       <c r="F91">
-        <v>209.506</v>
+        <v>211.86</v>
       </c>
       <c r="G91">
         <v>13.7</v>
@@ -8743,37 +8743,37 @@
         <v>16.929</v>
       </c>
       <c r="M91">
-        <v>49.4015148</v>
+        <v>49.956588</v>
       </c>
       <c r="N91">
-        <v>-32.4725148</v>
+        <v>-33.02758800000001</v>
       </c>
       <c r="O91">
-        <v>-8.767578996000001</v>
+        <v>-8.917448760000003</v>
       </c>
       <c r="P91">
-        <v>-23.704935804</v>
+        <v>-24.11013924000001</v>
       </c>
       <c r="Q91">
-        <v>-23.758935804</v>
+        <v>-24.16413924</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7180589245593749</v>
+        <v>0.7852848170153123</v>
       </c>
       <c r="T91">
-        <v>8.053488691590095</v>
+        <v>8.858837560749103</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09252408592134911</v>
+        <v>0.091496040522223</v>
       </c>
       <c r="W91">
-        <v>0.2139828205397459</v>
+        <v>0.2142252336448598</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3426817997087005</v>
+        <v>0.3388742241563815</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.271331191981905</v>
+        <v>0.273231191981905</v>
       </c>
       <c r="C92">
-        <v>-122.8688705956146</v>
+        <v>-125.8518658737984</v>
       </c>
       <c r="D92">
-        <v>75.29112940438537</v>
+        <v>74.66213412620158</v>
       </c>
       <c r="E92">
-        <v>38.96000000000001</v>
+        <v>41.31399999999999</v>
       </c>
       <c r="F92">
-        <v>211.86</v>
+        <v>214.214</v>
       </c>
       <c r="G92">
         <v>13.7</v>
@@ -8825,37 +8825,37 @@
         <v>16.929</v>
       </c>
       <c r="M92">
-        <v>49.956588</v>
+        <v>50.5116612</v>
       </c>
       <c r="N92">
-        <v>-33.02758800000001</v>
+        <v>-33.5826612</v>
       </c>
       <c r="O92">
-        <v>-8.917448760000003</v>
+        <v>-9.067318524000001</v>
       </c>
       <c r="P92">
-        <v>-24.11013924000001</v>
+        <v>-24.515342676</v>
       </c>
       <c r="Q92">
-        <v>-24.16413924</v>
+        <v>-24.569342676</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7852848170153123</v>
+        <v>0.8674497966836805</v>
       </c>
       <c r="T92">
-        <v>8.858837560749103</v>
+        <v>9.843152845276784</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.091496040522223</v>
+        <v>0.09049058952747331</v>
       </c>
       <c r="W92">
-        <v>0.2142252336448598</v>
+        <v>0.2144623189894218</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3388742241563815</v>
+        <v>0.3351503315832344</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.273231191981905</v>
+        <v>0.2751311919819051</v>
       </c>
       <c r="C93">
-        <v>-125.8518658737984</v>
+        <v>-128.8244387491837</v>
       </c>
       <c r="D93">
-        <v>74.66213412620158</v>
+        <v>74.04356125081627</v>
       </c>
       <c r="E93">
-        <v>41.31399999999999</v>
+        <v>43.66800000000001</v>
       </c>
       <c r="F93">
-        <v>214.214</v>
+        <v>216.568</v>
       </c>
       <c r="G93">
         <v>13.7</v>
@@ -8907,37 +8907,37 @@
         <v>16.929</v>
       </c>
       <c r="M93">
-        <v>50.5116612</v>
+        <v>51.0667344</v>
       </c>
       <c r="N93">
-        <v>-33.5826612</v>
+        <v>-34.1377344</v>
       </c>
       <c r="O93">
-        <v>-9.067318524000001</v>
+        <v>-9.217188288000001</v>
       </c>
       <c r="P93">
-        <v>-24.515342676</v>
+        <v>-24.920546112</v>
       </c>
       <c r="Q93">
-        <v>-24.569342676</v>
+        <v>-24.974546112</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8674497966836805</v>
+        <v>0.970156021269141</v>
       </c>
       <c r="T93">
-        <v>9.843152845276784</v>
+        <v>11.07354695093639</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09049058952747331</v>
+        <v>0.08950699616304425</v>
       </c>
       <c r="W93">
-        <v>0.2144623189894218</v>
+        <v>0.2146942503047542</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3351503315832344</v>
+        <v>0.3315073931964603</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2751311919819051</v>
+        <v>0.2770311919819051</v>
       </c>
       <c r="C94">
-        <v>-128.8244387491837</v>
+        <v>-131.7868461408109</v>
       </c>
       <c r="D94">
-        <v>74.04356125081627</v>
+        <v>73.4351538591891</v>
       </c>
       <c r="E94">
-        <v>43.66800000000001</v>
+        <v>46.02200000000002</v>
       </c>
       <c r="F94">
-        <v>216.568</v>
+        <v>218.922</v>
       </c>
       <c r="G94">
         <v>13.7</v>
@@ -8989,37 +8989,37 @@
         <v>16.929</v>
       </c>
       <c r="M94">
-        <v>51.0667344</v>
+        <v>51.62180760000001</v>
       </c>
       <c r="N94">
-        <v>-34.1377344</v>
+        <v>-34.69280760000001</v>
       </c>
       <c r="O94">
-        <v>-9.217188288000001</v>
+        <v>-9.367058052000003</v>
       </c>
       <c r="P94">
-        <v>-24.920546112</v>
+        <v>-25.325749548</v>
       </c>
       <c r="Q94">
-        <v>-24.974546112</v>
+        <v>-25.379749548</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.970156021269141</v>
+        <v>1.102206881450447</v>
       </c>
       <c r="T94">
-        <v>11.07354695093639</v>
+        <v>12.65548222964158</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08950699616304425</v>
+        <v>0.08854455534408677</v>
       </c>
       <c r="W94">
-        <v>0.2146942503047542</v>
+        <v>0.2149211938498644</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3315073931964603</v>
+        <v>0.3279427975706918</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2770311919819051</v>
+        <v>0.2789311919819051</v>
       </c>
       <c r="C95">
-        <v>-131.7868461408109</v>
+        <v>-134.7393365922443</v>
       </c>
       <c r="D95">
-        <v>73.4351538591891</v>
+        <v>72.83666340775569</v>
       </c>
       <c r="E95">
-        <v>46.02200000000002</v>
+        <v>48.376</v>
       </c>
       <c r="F95">
-        <v>218.922</v>
+        <v>221.276</v>
       </c>
       <c r="G95">
         <v>13.7</v>
@@ -9071,37 +9071,37 @@
         <v>16.929</v>
       </c>
       <c r="M95">
-        <v>51.62180760000001</v>
+        <v>52.17688080000001</v>
       </c>
       <c r="N95">
-        <v>-34.69280760000001</v>
+        <v>-35.2478808</v>
       </c>
       <c r="O95">
-        <v>-9.367058052000003</v>
+        <v>-9.516927816000003</v>
       </c>
       <c r="P95">
-        <v>-25.325749548</v>
+        <v>-25.730952984</v>
       </c>
       <c r="Q95">
-        <v>-25.379749548</v>
+        <v>-25.784952984</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.102206881450447</v>
+        <v>1.278274695025522</v>
       </c>
       <c r="T95">
-        <v>12.65548222964158</v>
+        <v>14.76472926791518</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08854455534408677</v>
+        <v>0.08760259198936246</v>
       </c>
       <c r="W95">
-        <v>0.2149211938498644</v>
+        <v>0.2151433088089083</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3279427975706918</v>
+        <v>0.3244540444050461</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2789311919819051</v>
+        <v>0.2808311919819051</v>
       </c>
       <c r="C96">
-        <v>-134.7393365922443</v>
+        <v>-137.6821506101105</v>
       </c>
       <c r="D96">
-        <v>72.83666340775569</v>
+        <v>72.24784938988955</v>
       </c>
       <c r="E96">
-        <v>48.376</v>
+        <v>50.73000000000002</v>
       </c>
       <c r="F96">
-        <v>221.276</v>
+        <v>223.63</v>
       </c>
       <c r="G96">
         <v>13.7</v>
@@ -9153,37 +9153,37 @@
         <v>16.929</v>
       </c>
       <c r="M96">
-        <v>52.17688080000001</v>
+        <v>52.73195400000001</v>
       </c>
       <c r="N96">
-        <v>-35.2478808</v>
+        <v>-35.80295400000001</v>
       </c>
       <c r="O96">
-        <v>-9.516927816000003</v>
+        <v>-9.666797580000004</v>
       </c>
       <c r="P96">
-        <v>-25.730952984</v>
+        <v>-26.13615642000001</v>
       </c>
       <c r="Q96">
-        <v>-25.784952984</v>
+        <v>-26.19015642000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.278274695025522</v>
+        <v>1.524769634030627</v>
       </c>
       <c r="T96">
-        <v>14.76472926791518</v>
+        <v>17.71767512149823</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08760259198936246</v>
+        <v>0.08668045944210599</v>
       </c>
       <c r="W96">
-        <v>0.2151433088089083</v>
+        <v>0.2153607476635514</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3244540444050461</v>
+        <v>0.3210387386744665</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2808311919819051</v>
+        <v>0.2827311919819051</v>
       </c>
       <c r="C97">
-        <v>-137.6821506101105</v>
+        <v>-140.6155209863473</v>
       </c>
       <c r="D97">
-        <v>72.24784938988955</v>
+        <v>71.66847901365274</v>
       </c>
       <c r="E97">
-        <v>50.73000000000002</v>
+        <v>53.08400000000003</v>
       </c>
       <c r="F97">
-        <v>223.63</v>
+        <v>225.984</v>
       </c>
       <c r="G97">
         <v>13.7</v>
@@ -9235,37 +9235,37 @@
         <v>16.929</v>
       </c>
       <c r="M97">
-        <v>52.73195400000001</v>
+        <v>53.28702720000001</v>
       </c>
       <c r="N97">
-        <v>-35.80295400000001</v>
+        <v>-36.35802720000001</v>
       </c>
       <c r="O97">
-        <v>-9.666797580000004</v>
+        <v>-9.816667344000003</v>
       </c>
       <c r="P97">
-        <v>-26.13615642000001</v>
+        <v>-26.54135985600001</v>
       </c>
       <c r="Q97">
-        <v>-26.19015642000001</v>
+        <v>-26.59535985600001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.524769634030627</v>
+        <v>1.894512042538284</v>
       </c>
       <c r="T97">
-        <v>17.71767512149823</v>
+        <v>22.1470939018728</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08668045944210599</v>
+        <v>0.08577753798958405</v>
       </c>
       <c r="W97">
-        <v>0.2153607476635514</v>
+        <v>0.2155736565420561</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3210387386744665</v>
+        <v>0.3176945851466076</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2827311919819051</v>
+        <v>0.2846311919819051</v>
       </c>
       <c r="C98">
-        <v>-140.6155209863472</v>
+        <v>-143.5396731050716</v>
       </c>
       <c r="D98">
-        <v>71.66847901365277</v>
+        <v>71.09832689492842</v>
       </c>
       <c r="E98">
-        <v>53.084</v>
+        <v>55.43799999999999</v>
       </c>
       <c r="F98">
-        <v>225.984</v>
+        <v>228.338</v>
       </c>
       <c r="G98">
         <v>13.7</v>
@@ -9317,37 +9317,37 @@
         <v>16.929</v>
       </c>
       <c r="M98">
-        <v>53.2870272</v>
+        <v>53.8421004</v>
       </c>
       <c r="N98">
-        <v>-36.35802720000001</v>
+        <v>-36.9131004</v>
       </c>
       <c r="O98">
-        <v>-9.816667344000003</v>
+        <v>-9.966537108000002</v>
       </c>
       <c r="P98">
-        <v>-26.54135985600001</v>
+        <v>-26.946563292</v>
       </c>
       <c r="Q98">
-        <v>-26.59535985600001</v>
+        <v>-27.000563292</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.894512042538279</v>
+        <v>2.510749390051039</v>
       </c>
       <c r="T98">
-        <v>22.14709390187274</v>
+        <v>29.52945853583032</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08577753798958407</v>
+        <v>0.08489323347422754</v>
       </c>
       <c r="W98">
-        <v>0.2155736565420561</v>
+        <v>0.2157821755467772</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3176945851466075</v>
+        <v>0.3144193832378797</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2846311919819051</v>
+        <v>0.286531191981905</v>
       </c>
       <c r="C99">
-        <v>-143.5396731050716</v>
+        <v>-146.4548252349149</v>
       </c>
       <c r="D99">
-        <v>71.09832689492842</v>
+        <v>70.53717476508513</v>
       </c>
       <c r="E99">
-        <v>55.43799999999999</v>
+        <v>57.792</v>
       </c>
       <c r="F99">
-        <v>228.338</v>
+        <v>230.692</v>
       </c>
       <c r="G99">
         <v>13.7</v>
@@ -9399,37 +9399,37 @@
         <v>16.929</v>
       </c>
       <c r="M99">
-        <v>53.8421004</v>
+        <v>54.3971736</v>
       </c>
       <c r="N99">
-        <v>-36.9131004</v>
+        <v>-37.4681736</v>
       </c>
       <c r="O99">
-        <v>-9.966537108000002</v>
+        <v>-10.116406872</v>
       </c>
       <c r="P99">
-        <v>-26.946563292</v>
+        <v>-27.351766728</v>
       </c>
       <c r="Q99">
-        <v>-27.000563292</v>
+        <v>-27.405766728</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.510749390051039</v>
+        <v>3.743224085076558</v>
       </c>
       <c r="T99">
-        <v>29.52945853583032</v>
+        <v>44.29418780374547</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08489323347422754</v>
+        <v>0.08402697598979664</v>
       </c>
       <c r="W99">
-        <v>0.2157821755467772</v>
+        <v>0.2159864390616059</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3144193832378797</v>
+        <v>0.3112110221844321</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.286531191981905</v>
+        <v>0.2884311919819051</v>
       </c>
       <c r="C100">
-        <v>-146.4548252349149</v>
+        <v>-149.3611888076234</v>
       </c>
       <c r="D100">
-        <v>70.53717476508513</v>
+        <v>69.98481119237654</v>
       </c>
       <c r="E100">
-        <v>57.792</v>
+        <v>60.14599999999999</v>
       </c>
       <c r="F100">
-        <v>230.692</v>
+        <v>233.046</v>
       </c>
       <c r="G100">
         <v>13.7</v>
@@ -9481,37 +9481,37 @@
         <v>16.929</v>
       </c>
       <c r="M100">
-        <v>54.3971736</v>
+        <v>54.9522468</v>
       </c>
       <c r="N100">
-        <v>-37.4681736</v>
+        <v>-38.0232468</v>
       </c>
       <c r="O100">
-        <v>-10.116406872</v>
+        <v>-10.266276636</v>
       </c>
       <c r="P100">
-        <v>-27.351766728</v>
+        <v>-27.75697016399999</v>
       </c>
       <c r="Q100">
-        <v>-27.405766728</v>
+        <v>-27.81097016399999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.743224085076558</v>
+        <v>7.440648170153116</v>
       </c>
       <c r="T100">
-        <v>44.29418780374547</v>
+        <v>88.58837560749095</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08402697598979664</v>
+        <v>0.08317821865656638</v>
       </c>
       <c r="W100">
-        <v>0.2159864390616059</v>
+        <v>0.2161865760407816</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3112110221844321</v>
+        <v>0.3080674765058015</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2884311919819051</v>
-      </c>
-      <c r="C101">
-        <v>-149.3611888076234</v>
-      </c>
-      <c r="D101">
-        <v>69.98481119237654</v>
-      </c>
-      <c r="E101">
-        <v>60.14599999999999</v>
-      </c>
-      <c r="F101">
-        <v>233.046</v>
-      </c>
-      <c r="G101">
-        <v>13.7</v>
-      </c>
-      <c r="H101">
-        <v>62.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>16.875</v>
-      </c>
-      <c r="K101">
-        <v>-0.054</v>
-      </c>
-      <c r="L101">
-        <v>16.929</v>
-      </c>
-      <c r="M101">
-        <v>54.9522468</v>
-      </c>
-      <c r="N101">
-        <v>-38.0232468</v>
-      </c>
-      <c r="O101">
-        <v>-10.266276636</v>
-      </c>
-      <c r="P101">
-        <v>-27.75697016399999</v>
-      </c>
-      <c r="Q101">
-        <v>-27.81097016399999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.440648170153116</v>
-      </c>
-      <c r="T101">
-        <v>88.58837560749095</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08317821865656638</v>
-      </c>
-      <c r="W101">
-        <v>0.2161865760407816</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3080674765058015</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
